--- a/store/vendors/AGL_Vendor_Signup_Playbook.xlsx
+++ b/store/vendors/AGL_Vendor_Signup_Playbook.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Batches" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Signups'!$A$1:$W$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Signups'!$A$1:$W$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Per app'!$A$1:$G$158</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-13 by scripts/signup_playbook.py. Re-run it any time; your columns are kept.</t>
+          <t>Generated 2026-10-14 by scripts/signup_playbook.py. Re-run it any time; your columns are kept.</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W101"/>
+  <dimension ref="A1:W104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2771,27 +2771,27 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>eCFR</t>
+          <t>CBP I-94</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>No public API — link to the official site</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>https://www.ecfr.gov/developers/documentation/api/v1</t>
+          <t>https://i94.cbp.dhs.gov/</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Exists — blocked automated check (bot-block page); open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Nothing to submit — public data. Respect the terms and attribution</t>
+          <t>Nothing</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -2809,11 +2809,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>PilotEnRoute</t>
-        </is>
-      </c>
+      <c r="K7" s="7" t="inlineStr"/>
       <c r="L7" s="7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
       <c r="N7" s="7" t="inlineStr"/>
@@ -2827,7 +2823,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q7" s="7" t="inlineStr"/>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>No scraping of government sites; the user enters their I-94 details</t>
+        </is>
+      </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
           <t>Not needed</t>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>FAA DroneZone</t>
+          <t>eCFR</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>https://faadronezone-access.faa.gov/</t>
+          <t>https://www.ecfr.gov/developers/documentation/api/v1</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>Exists — blocked automated check (bot-block page); open in a browser</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>FAA Safety Team (FAASTeam)</t>
+          <t>FAA DroneZone</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>https://www.faasafety.gov/</t>
+          <t>https://faadronezone-access.faa.gov/</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>FAA UAS</t>
+          <t>FAA Safety Team (FAASTeam)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>https://www.faa.gov/uas</t>
+          <t>https://www.faasafety.gov/</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -3052,12 +3052,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr"/>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>PilotEnRoute</t>
         </is>
       </c>
+      <c r="L10" s="7" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
       <c r="N10" s="7" t="inlineStr"/>
       <c r="O10" s="7" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Federal Aviation Administration (FAA)</t>
+          <t>FAA UAS</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>https://www.faa.gov/</t>
+          <t>https://www.faa.gov/uas</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -3133,12 +3133,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>PilotEnRoute</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="7" t="inlineStr"/>
       <c r="O11" s="7" t="inlineStr">
@@ -3176,47 +3176,47 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Federal Aviation Administration (FAA)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Deep links need no signup</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>https://www.lyft.com/developers</t>
+          <t>https://www.faa.gov/</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>OK — requires Lyft sign-in</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
+          <t>Nothing to submit — public data. Respect the terms and attribution</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>RideZap</t>
+          <t>PilotEnRoute</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr"/>
@@ -3224,7 +3224,7 @@
       <c r="N12" s="7" t="inlineStr"/>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
@@ -3235,7 +3235,7 @@
       <c r="Q12" s="7" t="inlineStr"/>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Not needed</t>
         </is>
       </c>
       <c r="S12" s="7" t="inlineStr"/>
@@ -3257,27 +3257,27 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>NASA ASRS</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Deep links need no signup</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>https://asrs.arc.nasa.gov/</t>
+          <t>https://www.lyft.com/developers</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK — requires Lyft sign-in</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Nothing to submit — public data. Respect the terms and attribution</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -3295,17 +3295,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>PilotEnRoute</t>
-        </is>
-      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>RideZap</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="7" t="inlineStr"/>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
@@ -3316,7 +3316,7 @@
       <c r="Q13" s="7" t="inlineStr"/>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>Not needed</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="S13" s="7" t="inlineStr"/>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>NOAA</t>
+          <t>NASA ASRS</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>https://www.weather.gov/documentation/services-web-api</t>
+          <t>https://asrs.arc.nasa.gov/</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -3376,12 +3376,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>iMaps</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr"/>
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>PilotEnRoute</t>
+        </is>
+      </c>
       <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="7" t="inlineStr"/>
       <c r="O14" s="7" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>NTSB</t>
+          <t>NOAA</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>https://www.ntsb.gov/</t>
+          <t>https://www.weather.gov/documentation/services-web-api</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://www.ntsb.gov/Pages/home.aspx</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -3457,12 +3457,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>PilotEnRoute</t>
-        </is>
-      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>iMaps</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="7" t="inlineStr"/>
       <c r="O15" s="7" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Open-Meteo</t>
+          <t>NTSB</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>https://open-meteo.com/</t>
+          <t>https://www.ntsb.gov/</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK (HTTP 200), lands on https://www.ntsb.gov/Pages/home.aspx</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -3538,12 +3538,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>daily-pulse; iMaps</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr"/>
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>PilotEnRoute</t>
+        </is>
+      </c>
       <c r="M16" s="7" t="inlineStr"/>
       <c r="N16" s="7" t="inlineStr"/>
       <c r="O16" s="7" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>OpenSky Network</t>
+          <t>Open-Meteo</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>https://opensky-network.org/</t>
+          <t>https://open-meteo.com/</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>HTTP 403 to automated check — open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>AeroSwift</t>
+          <t>daily-pulse; iMaps</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr"/>
@@ -3637,14 +3637,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>OpenSky: check commercial-use terms (AeroSwift shows ads)</t>
-        </is>
-      </c>
+      <c r="Q17" s="7" t="inlineStr"/>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Not needed</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr"/>
@@ -3666,7 +3662,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>OurAirports</t>
+          <t>OpenSky Network</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -3676,12 +3672,12 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>https://ourairports.com/data/</t>
+          <t>https://opensky-network.org/</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>No answer to automated check — open in a browser</t>
+          <t>HTTP 403 to automated check — open in a browser</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -3706,7 +3702,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute</t>
+          <t>AeroSwift</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr"/>
@@ -3722,10 +3718,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q18" s="7" t="inlineStr"/>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>OpenSky: check commercial-use terms (AeroSwift shows ads)</t>
+        </is>
+      </c>
       <c r="R18" s="7" t="inlineStr">
         <is>
-          <t>Not needed</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr"/>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Rotate Pilot</t>
+          <t>OurAirports</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>https://rotatepilot.com/</t>
+          <t>https://ourairports.com/data/</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>No answer to automated check — open in a browser</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>SEC EDGAR</t>
+          <t>Rotate Pilot</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/search-filings/edgar-application-programming-interfaces</t>
+          <t>https://rotatepilot.com/</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>HTTP 403 to automated check — open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>ApexMarketWatch</t>
+          <t>PilotEnRoute</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr"/>
@@ -3909,43 +3909,47 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>SEC EDGAR</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Deep links need no signup</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr"/>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/search-filings/edgar-application-programming-interfaces</t>
+        </is>
+      </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
+          <t>HTTP 403 to automated check — open in a browser</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Nothing to submit — public data. Respect the terms and attribution</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>RideZap</t>
+          <t>ApexMarketWatch</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr"/>
@@ -3953,22 +3957,18 @@
       <c r="N21" s="7" t="inlineStr"/>
       <c r="O21" s="7" t="inlineStr">
         <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>Deep links need no signup; developer.uber.com returned 404. Consumer affiliate availability not verified</t>
-        </is>
-      </c>
+      <c r="Q21" s="7" t="inlineStr"/>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Not needed</t>
         </is>
       </c>
       <c r="S21" s="7" t="inlineStr"/>
@@ -3978,59 +3978,55 @@
       <c r="W21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>1 Travelpayouts (TripNest)</t>
+          <t>0 No signup</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Booking.com Demand API</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>For TripNest: join inside Travelpayouts (Programs). Direct programme only if you want it outside Travelpayouts</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/affiliate-program/v2/index.html</t>
-        </is>
-      </c>
+          <t>Deep links need no signup</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr"/>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Join request inside Travelpayouts (uses your Travelpayouts profile)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Brand approval under your Travelpayouts marker</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Travelpayouts → Programs → Booking.com</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Nothing new — the Travelpayouts marker covers it</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>RideZap</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr"/>
@@ -4038,15 +4034,19 @@
       <c r="N22" s="7" t="inlineStr"/>
       <c r="O22" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>Brand reviews the request</t>
-        </is>
-      </c>
-      <c r="Q22" s="7" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>Deep links need no signup; developer.uber.com returned 404. Consumer affiliate availability not verified</t>
+        </is>
+      </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Busbud</t>
+          <t>Booking.com Demand API</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>https://www.busbud.com/</t>
+          <t>https://www.booking.com/affiliate-program/v2/index.html</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://www.busbud.com/en</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Travelpayouts → Programs → Busbud</t>
+          <t>Travelpayouts → Programs → Booking.com</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Busbud</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>https://affiliates.expediagroup.com/</t>
+          <t>https://www.busbud.com/</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://creator.expediagroup.com/</t>
+          <t>OK (HTTP 200), lands on https://www.busbud.com/en</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Travelpayouts → Programs → Expedia</t>
+          <t>Travelpayouts → Programs → Busbud</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
@@ -4208,11 +4208,7 @@
           <t>Brand reviews the request</t>
         </is>
       </c>
-      <c r="Q24" s="7" t="inlineStr">
-        <is>
-          <t>affiliates.expediagroup.com now lands on creator.expediagroup.com (Expedia Group affiliate/creator programme). For TripNest join via Travelpayouts.</t>
-        </is>
-      </c>
+      <c r="Q24" s="7" t="inlineStr"/>
       <c r="R24" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -4237,7 +4233,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Rentalcars.com</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -4247,12 +4243,12 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>https://www.rentalcars.com/</t>
+          <t>https://affiliates.expediagroup.com/</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK (HTTP 200), lands on https://creator.expediagroup.com/</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -4267,7 +4263,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Travelpayouts → Programs → Rentalcars.com</t>
+          <t>Travelpayouts → Programs → Expedia</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -4293,7 +4289,11 @@
           <t>Brand reviews the request</t>
         </is>
       </c>
-      <c r="Q25" s="7" t="inlineStr"/>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>affiliates.expediagroup.com now lands on creator.expediagroup.com (Expedia Group affiliate/creator programme). For TripNest join via Travelpayouts.</t>
+        </is>
+      </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -4318,17 +4318,17 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Travelpayouts</t>
+          <t>Rentalcars.com</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Direct account</t>
+          <t>For TripNest: join inside Travelpayouts (Programs). Direct programme only if you want it outside Travelpayouts</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>https://www.travelpayouts.com/</t>
+          <t>https://www.rentalcars.com/</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -4338,22 +4338,22 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9; select the travel brands to join</t>
+          <t>Join request inside Travelpayouts (uses your Travelpayouts profile)</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Numeric marker (partner ID); per-brand approval</t>
+          <t>Brand approval under your Travelpayouts marker</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>Dashboard → Profile/Tools: your numeric 'marker' (partner ID); Programs → join each brand</t>
+          <t>Travelpayouts → Programs → Rentalcars.com</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>TRIPNEST_AFFILIATE_MARKER build define (TripNest)</t>
+          <t>Nothing new — the Travelpayouts marker covers it</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -4363,11 +4363,7 @@
       </c>
       <c r="L26" s="7" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>TripNest: marker 'americangroupllc' — Travelpayouts markers are numeric</t>
-        </is>
-      </c>
+      <c r="N26" s="7" t="inlineStr"/>
       <c r="O26" s="7" t="inlineStr">
         <is>
           <t>Free</t>
@@ -4375,14 +4371,10 @@
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>Account instant; brands approve individually</t>
-        </is>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
-        <is>
-          <t>TripNest currently sends marker 'americangroupllc', which is not a numeric marker</t>
-        </is>
-      </c>
+          <t>Brand reviews the request</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr"/>
       <c r="R26" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -4407,17 +4399,17 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Viator</t>
+          <t>Travelpayouts</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>For TripNest: join inside Travelpayouts (Programs). Direct programme only if you want it outside Travelpayouts</t>
+          <t>Direct account</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>https://partnerresources.viator.com/</t>
+          <t>https://www.travelpayouts.com/</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -4427,22 +4419,22 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Join request inside Travelpayouts (uses your Travelpayouts profile)</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9; select the travel brands to join</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Brand approval under your Travelpayouts marker</t>
+          <t>Numeric marker (partner ID); per-brand approval</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>Travelpayouts → Programs → Viator</t>
+          <t>Dashboard → Profile/Tools: your numeric 'marker' (partner ID); Programs → join each brand</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>Nothing new — the Travelpayouts marker covers it</t>
+          <t>TRIPNEST_AFFILIATE_MARKER build define (TripNest)</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -4452,7 +4444,11 @@
       </c>
       <c r="L27" s="7" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>TripNest: marker 'americangroupllc' — Travelpayouts markers are numeric</t>
+        </is>
+      </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
           <t>Free</t>
@@ -4460,10 +4456,14 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>Brand reviews the request</t>
-        </is>
-      </c>
-      <c r="Q27" s="7" t="inlineStr"/>
+          <t>Account instant; brands approve individually</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>TripNest currently sends marker 'americangroupllc', which is not a numeric marker</t>
+        </is>
+      </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -4483,22 +4483,22 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>2 Retail affiliates</t>
+          <t>1 Travelpayouts (TripNest)</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Amazon Associates</t>
+          <t>Viator</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>For TripNest: join inside Travelpayouts (Programs). Direct programme only if you want it outside Travelpayouts</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>https://affiliate-program.amazon.com/</t>
+          <t>https://partnerresources.viator.com/</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -4508,36 +4508,32 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9; list each app as a 'mobile app' property</t>
+          <t>Join request inside Travelpayouts (uses your Travelpayouts profile)</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Store ID + one tracking ID per app (format name-20)</t>
+          <t>Brand approval under your Travelpayouts marker</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>Associates Central → Account → Manage Your Tracking IDs (create one per app)</t>
+          <t>Travelpayouts → Programs → Viator</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>AGL_AFFILIATE_TAGS / per-app tag build define (CalcMaster, ChefCount, VirtuBand)</t>
+          <t>Nothing new — the Travelpayouts marker covers it</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>CalcMaster; ChefCount; VirtuBand</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>CalcMaster: hard-coded calcmaster-20/-21, marked REPLACE in code | ChefCount: tag 'americangroupllc' — not a valid store-ID format | VirtuBand: hard-coded tag virtuband-20 — registration not verified</t>
-        </is>
-      </c>
+      <c r="N28" s="7" t="inlineStr"/>
       <c r="O28" s="7" t="inlineStr">
         <is>
           <t>Free</t>
@@ -4545,14 +4541,10 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>Provisional; Amazon reviews after the first qualifying sales</t>
-        </is>
-      </c>
-      <c r="Q28" s="7" t="inlineStr">
-        <is>
-          <t>Amazon closes accounts with no qualifying sales in the first 180 days — confirm current rule on the page</t>
-        </is>
-      </c>
+          <t>Brand reviews the request</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr"/>
       <c r="R28" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -4577,17 +4569,17 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Rakuten Advertising</t>
+          <t>Amazon Associates</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Publisher network</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>https://rakutenadvertising.com/publishers/</t>
+          <t>https://affiliate-program.amazon.com/</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -4597,32 +4589,36 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9; list each app as a 'mobile app' property</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Publisher Site ID; per-advertiser approval</t>
+          <t>Store ID + one tracking ID per app (format name-20)</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>Publisher dashboard → Account → Site ID; Advertisers → apply to each brand</t>
+          <t>Associates Central → Account → Manage Your Tracking IDs (create one per app)</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>AGL_AFFILIATE_TAGS (FashionFactory, VirtuBand)</t>
+          <t>AGL_AFFILIATE_TAGS / per-app tag build define (CalcMaster, ChefCount, VirtuBand)</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>VirtuBand</t>
+          <t>CalcMaster; ChefCount; VirtuBand</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>CalcMaster: hard-coded calcmaster-20/-21, marked REPLACE in code | ChefCount: tag 'americangroupllc' — not a valid store-ID format | VirtuBand: hard-coded tag virtuband-20 — registration not verified</t>
+        </is>
+      </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
           <t>Free</t>
@@ -4630,10 +4626,14 @@
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>Network review, then each advertiser</t>
-        </is>
-      </c>
-      <c r="Q29" s="7" t="inlineStr"/>
+          <t>Provisional; Amazon reviews after the first qualifying sales</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>Amazon closes accounts with no qualifying sales in the first 180 days — confirm current rule on the page</t>
+        </is>
+      </c>
       <c r="R29" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -4646,9 +4646,9 @@
       <c r="W29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>P4</t>
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -4658,55 +4658,55 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Awin</t>
+          <t>Rakuten Advertising</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Publisher network (ShareASale is now part of Awin)</t>
+          <t>Publisher network</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>https://www.awin.com/us/publishers</t>
+          <t>https://rakutenadvertising.com/publishers/</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://www.awin.com/us/publishers/content-creator-influencer</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9; Awin may ask a small refundable deposit — confirm on the page</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Publisher ID; per-advertiser approval</t>
+          <t>Publisher Site ID; per-advertiser approval</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Awin UI → Account → Publisher ID; Advertisers → join programmes</t>
+          <t>Publisher dashboard → Account → Site ID; Advertisers → apply to each brand</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>AGL_AFFILIATE_TAGS (FashionFactory)</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>FashionFactory; TripNest</t>
-        </is>
-      </c>
+          <t>AGL_AFFILIATE_TAGS (FashionFactory, VirtuBand)</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>VirtuBand</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
       <c r="N30" s="7" t="inlineStr"/>
       <c r="O30" s="7" t="inlineStr">
         <is>
-          <t>Free (refundable deposit may apply)</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
@@ -4739,60 +4739,60 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Best Buy Affiliate Program</t>
+          <t>Awin</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Via an affiliate network (network not verified — check bestbuy.com footer 'Affiliate Program')</t>
+          <t>Publisher network (ShareASale is now part of Awin)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>https://www.bestbuy.com/</t>
+          <t>https://www.awin.com/us/publishers</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>No answer to automated check — open in a browser</t>
+          <t>OK (HTTP 200), lands on https://www.awin.com/us/publishers/content-creator-influencer</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9; Awin may ask a small refundable deposit — confirm on the page</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>Network publisher ID + Best Buy approval</t>
+          <t>Publisher ID; per-advertiser approval</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>bestbuy.com → footer → Affiliate Program → network sign-in</t>
+          <t>Awin UI → Account → Publisher ID; Advertisers → join programmes</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>GadgetNest retailer links</t>
+          <t>AGL_AFFILIATE_TAGS (FashionFactory)</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr"/>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>GadgetNest</t>
+          <t>FashionFactory; TripNest</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="7" t="inlineStr"/>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free (refundable deposit may apply)</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>Brand review</t>
+          <t>Network review, then each advertiser</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr"/>
@@ -4820,22 +4820,22 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>CJ Affiliate</t>
+          <t>Best Buy Affiliate Program</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Publisher network</t>
+          <t>Via an affiliate network (network not verified — check bestbuy.com footer 'Affiliate Program')</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>https://public.cj.com/signup/publisher</t>
+          <t>https://www.bestbuy.com/</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>No answer to automated check — open in a browser</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -4845,23 +4845,23 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Publisher ID (PID) + website ID; per-advertiser approval</t>
+          <t>Network publisher ID + Best Buy approval</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>CJ Account Manager → Account → Publisher ID (PID); Advertisers → apply</t>
+          <t>bestbuy.com → footer → Affiliate Program → network sign-in</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>Per-app build define once an app uses CJ links</t>
+          <t>GadgetNest retailer links</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr"/>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>TripNest; CodeDeal; GadgetNest</t>
+          <t>GadgetNest</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr"/>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>Network review, then each advertiser</t>
+          <t>Brand review</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr"/>
@@ -4901,17 +4901,17 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>eBay Partner Network</t>
+          <t>CJ Affiliate</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Publisher network</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>https://partnernetwork.ebay.com/</t>
+          <t>https://public.cj.com/signup/publisher</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -4926,23 +4926,23 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Campaign ID (campid)</t>
+          <t>Publisher ID (PID) + website ID; per-advertiser approval</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>EPN → Campaigns → create a campaign per app (campid)</t>
+          <t>CJ Account Manager → Account → Publisher ID (PID); Advertisers → apply</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>GadgetNest retailer links</t>
+          <t>Per-app build define once an app uses CJ links</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr"/>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>GadgetNest</t>
+          <t>TripNest; CodeDeal; GadgetNest</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr"/>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>Usually quick; payouts after review</t>
+          <t>Network review, then each advertiser</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr"/>
@@ -4982,17 +4982,17 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>FlexOffers</t>
+          <t>eBay Partner Network</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Publisher network</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>https://www.flexoffers.com/</t>
+          <t>https://partnernetwork.ebay.com/</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -5007,21 +5007,25 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Publisher ID</t>
+          <t>Campaign ID (campid)</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>FlexOffers dashboard → domain/app ID</t>
+          <t>EPN → Campaigns → create a campaign per app (campid)</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>Any app that adds FlexOffers links</t>
+          <t>GadgetNest retailer links</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>GadgetNest</t>
+        </is>
+      </c>
       <c r="M34" s="7" t="inlineStr"/>
       <c r="N34" s="7" t="inlineStr"/>
       <c r="O34" s="7" t="inlineStr">
@@ -5031,7 +5035,7 @@
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>Network review</t>
+          <t>Usually quick; payouts after review</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr"/>
@@ -5059,17 +5063,17 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>FlexOffers</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Partner network (impact.com)</t>
+          <t>Publisher network</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>https://impact.com/partners/</t>
+          <t>https://www.flexoffers.com/</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -5084,25 +5088,21 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>Partner/Media Partner ID + per-brand tracking links</t>
+          <t>Publisher ID</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>impact.com partner dashboard → Settings → Account ID; Brands → apply (DoorDash, Uber Eats, Grubhub, Walmart, Best Buy… verify which are on impact)</t>
+          <t>FlexOffers dashboard → domain/app ID</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>Per-brand affiliate ID defines (GroceryMatch delivery links when restored)</t>
+          <t>Any app that adds FlexOffers links</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>GroceryMatch; MyHealth; TripNest</t>
-        </is>
-      </c>
+      <c r="L35" s="7" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
       <c r="N35" s="7" t="inlineStr"/>
       <c r="O35" s="7" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>Network review, then each brand</t>
+          <t>Network review</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr"/>
@@ -5140,67 +5140,63 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>ShareASale</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Now inside Awin — apply via Awin</t>
+          <t>Partner network (impact.com)</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>https://www.shareasale.com/</t>
+          <t>https://impact.com/partners/</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://www.awin.com/us/getting-started-sas?utm_medium=redirect&amp;utm_source=www.shareasale.com</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Use the Awin application</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Partner/Media Partner ID + per-brand tracking links</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>impact.com partner dashboard → Settings → Account ID; Brands → apply (DoorDash, Uber Eats, Grubhub, Walmart, Best Buy… verify which are on impact)</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Per-brand affiliate ID defines (GroceryMatch delivery links when restored)</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr"/>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>FashionFactory</t>
+          <t>GroceryMatch; MyHealth; TripNest</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr"/>
       <c r="N36" s="7" t="inlineStr"/>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q36" s="7" t="inlineStr">
-        <is>
-          <t>ShareASale merchants are reached through Awin</t>
-        </is>
-      </c>
+          <t>Network review, then each brand</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr"/>
       <c r="R36" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -5225,63 +5221,67 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Walmart Affiliates</t>
+          <t>ShareASale</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Direct site (runs on a network — confirm on the page)</t>
+          <t>Now inside Awin — apply via Awin</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>https://affiliates.walmart.com/</t>
+          <t>https://www.shareasale.com/</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK (HTTP 200), lands on https://www.awin.com/us/getting-started-sas?utm_medium=redirect&amp;utm_source=www.shareasale.com</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Use the Awin application</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>Affiliate ID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Walmart affiliate dashboard → tracking/ID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>GadgetNest / GroceryMatch retailer links</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr"/>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>GroceryMatch; GadgetNest</t>
+          <t>FashionFactory</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr"/>
       <c r="N37" s="7" t="inlineStr"/>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>Brand review</t>
-        </is>
-      </c>
-      <c r="Q37" s="7" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>ShareASale merchants are reached through Awin</t>
+        </is>
+      </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -5294,64 +5294,64 @@
       <c r="W37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>P4</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>3 Google Cloud console</t>
+          <t>2 Retail affiliates</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Google AdMob</t>
+          <t>Walmart Affiliates</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Existing account</t>
+          <t>Direct site (runs on a network — confirm on the page)</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>https://admob.google.com/</t>
+          <t>https://affiliates.walmart.com/</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://admob.google.com/home/</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>App name, platform, store listing (after release)</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>AdMob app ID (ca-app-pub-…~…) and ad unit IDs</t>
+          <t>Affiliate ID</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>Apps → Add app → per app per platform; link the store listing when live</t>
+          <t>Walmart affiliate dashboard → tracking/ID</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>docs/admob-ids.json (already holds units)</t>
+          <t>GadgetNest / GroceryMatch retailer links</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr"/>
-      <c r="L38" s="7" t="inlineStr"/>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>GroceryMatch; GadgetNest</t>
+        </is>
+      </c>
       <c r="M38" s="7" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr">
-        <is>
-          <t>account exists; ad units in docs/admob-ids.json; AdMob apps still to create in the UI (#15)</t>
-        </is>
-      </c>
+      <c r="N38" s="7" t="inlineStr"/>
       <c r="O38" s="7" t="inlineStr">
         <is>
           <t>Free</t>
@@ -5359,17 +5359,13 @@
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
-        </is>
-      </c>
-      <c r="Q38" s="7" t="inlineStr">
-        <is>
-          <t>Issue #15: the AdMob apps must be created in the UI</t>
-        </is>
-      </c>
+          <t>Brand review</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr"/>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr"/>
@@ -5391,58 +5387,50 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Google Sign-In (OAuth client, iOS)</t>
+          <t>Google AdMob</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Google Cloud project (existing)</t>
+          <t>Existing account</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>https://console.cloud.google.com/apis/credentials</t>
+          <t>https://admob.google.com/</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>OK — requires Google sign-in (expected)</t>
+          <t>OK (HTTP 200), lands on https://admob.google.com/home/</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Bundle id per app (from status.csv), app name, OAuth consent screen (support email, privacy URL, authorised domain americangroup.ai)</t>
+          <t>App name, platform, store listing (after release)</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>iOS client ID (…apps.googleusercontent.com) + reversed client ID</t>
+          <t>AdMob app ID (ca-app-pub-…~…) and ad unit IDs</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>APIs &amp; Services → Credentials → Create credentials → OAuth client ID → iOS → enter each app's bundle id</t>
+          <t>Apps → Add app → per app per platform; link the store listing when live</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>GOOGLE_IOS_CLIENT_ID define, Info.plist URL scheme (reversed id), Supabase Auth → Google → authorised client IDs</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>CalcMaster; DriftDate; PilotEnRoute; Uscis-Case; iMaps; iMeasure; radiotune</t>
-        </is>
-      </c>
+          <t>docs/admob-ids.json (already holds units)</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr"/>
       <c r="L39" s="7" t="inlineStr"/>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>GOOGLE_IOS_CLIENT_ID</t>
-        </is>
-      </c>
+      <c r="M39" s="7" t="inlineStr"/>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>CalcMaster: EMPTY in release | DriftDate: EMPTY in release | iMaps: EMPTY in release | iMeasure: EMPTY in release | PilotEnRoute: EMPTY in release | radiotune: EMPTY in release | Uscis-Case: EMPTY in release</t>
+          <t>account exists; ad units in docs/admob-ids.json; AdMob apps still to create in the UI (#15)</t>
         </is>
       </c>
       <c r="O39" s="7" t="inlineStr">
@@ -5452,17 +5440,17 @@
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>Instant (consent screen verification may take days for sensitive scopes)</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>Needed by CalcMaster, DriftDate, PilotEnRoute, Uscis-Case, iMaps, iMeasure, radiotune</t>
+          <t>Issue #15: the AdMob apps must be created in the UI</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="S39" s="7" t="inlineStr"/>
@@ -5472,9 +5460,9 @@
       <c r="W39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>P4</t>
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -5484,63 +5472,75 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Google AI</t>
+          <t>Google Sign-In (OAuth client, iOS)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Google AI Studio / Vertex</t>
+          <t>Google Cloud project (existing)</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>https://aistudio.google.com/</t>
+          <t>https://console.cloud.google.com/apis/credentials</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://aistudio.google.com/welcome</t>
+          <t>OK — requires Google sign-in (expected)</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Bundle id per app (from status.csv), app name, OAuth consent screen (support email, privacy URL, authorised domain americangroup.ai)</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>iOS client ID (…apps.googleusercontent.com) + reversed client ID</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>AI Studio → Get API key</t>
+          <t>APIs &amp; Services → Credentials → Create credentials → OAuth client ID → iOS → enter each app's bundle id</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>PlantPulse; AGStudio</t>
-        </is>
-      </c>
-      <c r="M40" s="7" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
+          <t>GOOGLE_IOS_CLIENT_ID define, Info.plist URL scheme (reversed id), Supabase Auth → Google → authorised client IDs</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>CalcMaster; DriftDate; PilotEnRoute; Uscis-Case; iMaps; iMeasure; radiotune</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>GOOGLE_IOS_CLIENT_ID</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>CalcMaster: EMPTY in release | DriftDate: EMPTY in release | iMaps: EMPTY in release | iMeasure: EMPTY in release | PilotEnRoute: EMPTY in release | radiotune: EMPTY in release | Uscis-Case: EMPTY in release</t>
+        </is>
+      </c>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>Free tier + usage</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
-        </is>
-      </c>
-      <c r="Q40" s="7" t="inlineStr"/>
+          <t>Instant (consent screen verification may take days for sensitive scopes)</t>
+        </is>
+      </c>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>Needed by CalcMaster, DriftDate, PilotEnRoute, Uscis-Case, iMaps, iMeasure, radiotune</t>
+        </is>
+      </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -5565,55 +5565,55 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Google Maps Platform</t>
+          <t>Google AI</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Google Cloud project</t>
+          <t>Google AI Studio / Vertex</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>https://console.cloud.google.com/google/maps-apis/</t>
+          <t>https://aistudio.google.com/</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>OK — requires Google sign-in (expected)</t>
+          <t>OK (HTTP 200), lands on https://aistudio.google.com/welcome</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Billing account on the project</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>API key (restricted per platform)</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>Maps Platform → Keys &amp; Credentials → Create API key → restrict to iOS bundle ids / Android package+SHA-1</t>
+          <t>AI Studio → Get API key</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>Per-app maps key define / Info.plist / AndroidManifest</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr"/>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>GroceryMatch; Kinnav; NearServe; iMaps</t>
+          <t>PlantPulse; AGStudio</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr"/>
       <c r="N41" s="7" t="inlineStr"/>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>Usage-based with free monthly credit</t>
+          <t>Free tier + usage</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
@@ -5634,80 +5634,72 @@
       <c r="W41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>P4</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>4 Free data keys</t>
+          <t>3 Google Cloud console</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>NASA FIRMS</t>
+          <t>Google Maps Platform</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Google Cloud project</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>https://firms.modaps.eosdis.nasa.gov/api/map_key/</t>
+          <t>https://console.cloud.google.com/google/maps-apis/</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK — requires Google sign-in (expected)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>Email address</t>
+          <t>Billing account on the project</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>MAP_KEY</t>
+          <t>API key (restricted per platform)</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>Enter email → MAP_KEY emailed</t>
+          <t>Maps Platform → Keys &amp; Credentials → Create API key → restrict to iOS bundle ids / Android package+SHA-1</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>NASA_FIRMS_KEY define (iMaps)</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
-          <t>iMaps</t>
-        </is>
-      </c>
-      <c r="L42" s="7" t="inlineStr"/>
-      <c r="M42" s="7" t="inlineStr">
-        <is>
-          <t>NASA_FIRMS_KEY</t>
-        </is>
-      </c>
-      <c r="N42" s="7" t="inlineStr">
-        <is>
-          <t>iMaps: NASA_FIRMS_KEY: EMPTY in release</t>
-        </is>
-      </c>
+          <t>Per-app maps key define / Info.plist / AndroidManifest</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>GroceryMatch; Kinnav; NearServe; iMaps</t>
+        </is>
+      </c>
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Usage-based with free monthly credit</t>
         </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>Instant (email)</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr"/>
@@ -5735,7 +5727,7 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Open Charge Map</t>
+          <t>NASA FIRMS</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -5745,32 +5737,32 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>https://openchargemap.org/site/develop/api</t>
+          <t>https://firms.modaps.eosdis.nasa.gov/api/map_key/</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://openchargemap.org/loginprovider/beginlogin</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Account, app name and URL</t>
+          <t>Email address</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>MAP_KEY</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>Sign in → My Profile → API keys → Register an application</t>
+          <t>Enter email → MAP_KEY emailed</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>OPENCHARGEMAP_KEY define (iMaps)</t>
+          <t>NASA_FIRMS_KEY define (iMaps)</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
@@ -5781,12 +5773,12 @@
       <c r="L43" s="7" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>OPENCHARGEMAP_KEY</t>
+          <t>NASA_FIRMS_KEY</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>iMaps: OPENCHARGEMAP_KEY: EMPTY in release</t>
+          <t>iMaps: NASA_FIRMS_KEY: EMPTY in release</t>
         </is>
       </c>
       <c r="O43" s="7" t="inlineStr">
@@ -5796,7 +5788,7 @@
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Instant (email)</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr"/>
@@ -5812,9 +5804,9 @@
       <c r="W43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -5824,42 +5816,42 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>NREL / NLR alt-fuel</t>
+          <t>Open Charge Map</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>api.data.gov key (one key for many US gov APIs)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>https://api.data.gov/signup/</t>
+          <t>https://openchargemap.org/site/develop/api</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK (HTTP 200), lands on https://openchargemap.org/loginprovider/beginlogin</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>Name, email</t>
+          <t>Account, app name and URL</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>api.data.gov key (replaces DEMO_KEY)</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>Form → key emailed</t>
+          <t>Sign in → My Profile → API keys → Register an application</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>NREL_API_KEY (iMaps), USDA_API_KEY</t>
+          <t>OPENCHARGEMAP_KEY define (iMaps)</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
@@ -5870,12 +5862,12 @@
       <c r="L44" s="7" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>NREL_API_KEY</t>
+          <t>OPENCHARGEMAP_KEY</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>iMaps: NREL_API_KEY: default set</t>
+          <t>iMaps: OPENCHARGEMAP_KEY: EMPTY in release</t>
         </is>
       </c>
       <c r="O44" s="7" t="inlineStr">
@@ -5901,29 +5893,29 @@
       <c r="W44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>5 AI / server-side keys</t>
+          <t>4 Free data keys</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>NREL / NLR alt-fuel</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>api.data.gov key (one key for many US gov APIs)</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>https://platform.claude.com/</t>
+          <t>https://api.data.gov/signup/</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -5933,43 +5925,43 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Name, email</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>api.data.gov key (replaces DEMO_KEY)</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>Claude Console (platform.claude.com) → API Keys → Create key</t>
+          <t>Form → key emailed</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret (PilotEnRoute calls the function) — never in the app</t>
+          <t>NREL_API_KEY (iMaps), USDA_API_KEY</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute</t>
+          <t>iMaps</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>ANTHROPIC_API_KEY</t>
+          <t>NREL_API_KEY</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute: ANTHROPIC_API_KEY: EMPTY in release</t>
+          <t>iMaps: NREL_API_KEY: default set</t>
         </is>
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>Usage-based (prepaid credits)</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
@@ -5990,9 +5982,9 @@
       <c r="W45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -6002,7 +5994,7 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>RevenueCat</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -6012,7 +6004,7 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>https://app.revenuecat.com/signup</t>
+          <t>https://platform.claude.com/</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -6022,35 +6014,43 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers; App Store Connect shared secret / in-app purchase key, Play service account</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>Public SDK keys per platform</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Project → Apps → add iOS/Android → public SDK keys</t>
+          <t>Claude Console (platform.claude.com) → API Keys → Create key</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>CalcMaster revenueCat key define</t>
+          <t>Supabase Edge Function secret (PilotEnRoute calls the function) — never in the app</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>CalcMaster</t>
+          <t>PilotEnRoute</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr"/>
-      <c r="M46" s="7" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>ANTHROPIC_API_KEY</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>PilotEnRoute: ANTHROPIC_API_KEY: EMPTY in release</t>
+        </is>
+      </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>Free up to a revenue threshold</t>
+          <t>Usage-based (prepaid credits)</t>
         </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
@@ -6071,9 +6071,9 @@
       <c r="W46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>P4</t>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>OpenAI API</t>
+          <t>RevenueCat</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -6093,45 +6093,45 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>https://platform.openai.com/signup</t>
+          <t>https://app.revenuecat.com/signup</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>HTTP 403 to automated check — open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers; App Store Connect shared secret / in-app purchase key, Play service account</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Public SDK keys per platform</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>Dashboard → API keys → Create</t>
+          <t>Project → Apps → add iOS/Android → public SDK keys</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr"/>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>Photriya; HerJourney; daily-pulse</t>
-        </is>
-      </c>
+          <t>CalcMaster revenueCat key define</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>CalcMaster</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
       <c r="N47" s="7" t="inlineStr"/>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>Usage-based</t>
+          <t>Free up to a revenue threshold</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
@@ -6152,29 +6152,29 @@
       <c r="W47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>6 Optional monitoring</t>
+          <t>5 AI / server-side keys</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>USCIS Developer Portal (Case Status API)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Founder's developer.uscis.gov account (exists) → register an app → request Case Status API access</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>https://sentry.io/signup/</t>
+          <t>https://developer.uscis.gov/</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -6184,53 +6184,41 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>App name and description (Uscis-Case), use case (show a user their own case status by receipt number), privacy policy URL https://www.americangroup.ai/policy/uscis-case-tracker/, company details</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>DSN</t>
+          <t>OAuth2 client ID + client secret (sandbox, then production)</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>Project → Settings → Client Keys (DSN)</t>
+          <t>Developer portal → My Apps → your app → client ID / secret (sandbox first; production after USCIS approves the use case)</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>SENTRY_DSN define (DriftDate, NexusTransferPay)</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>DriftDate; NexusTransferPay</t>
-        </is>
-      </c>
+          <t>Supabase Edge Function secrets (uscis-case-status) — never in the app, chat or git</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr"/>
       <c r="L48" s="7" t="inlineStr"/>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>SENTRY_DSN</t>
-        </is>
-      </c>
-      <c r="N48" s="7" t="inlineStr">
-        <is>
-          <t>DriftDate: SENTRY_DSN: EMPTY in release | NexusTransferPay: SENTRY_DSN: EMPTY in release</t>
-        </is>
-      </c>
+      <c r="M48" s="7" t="inlineStr"/>
+      <c r="N48" s="7" t="inlineStr"/>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Verify on the portal</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Sandbox on registration; production after USCIS review (verify)</t>
         </is>
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>Optional — Crashlytics already covers crashes</t>
+          <t>Spec: ai-office/projects/real-apps/specs/Uscis-Case-v2.md. The portal username stays in the founder vault, not in this file.</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
@@ -6252,12 +6240,12 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>6 Optional monitoring</t>
+          <t>5 AI / server-side keys</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>PostHog</t>
+          <t>OpenAI API</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -6267,12 +6255,12 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>https://us.posthog.com/signup</t>
+          <t>https://platform.openai.com/signup</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>HTTP 403 to automated check — open in a browser</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -6282,30 +6270,30 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Project key</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Project settings → Project API key</t>
+          <t>Dashboard → API keys → Create</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>POSTHOG_API_KEY (MyHealth)</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr"/>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>MyHealth</t>
+          <t>Photriya; HerJourney; daily-pulse</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr"/>
       <c r="N49" s="7" t="inlineStr"/>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Usage-based</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
@@ -6313,11 +6301,7 @@
           <t>Instant</t>
         </is>
       </c>
-      <c r="Q49" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
+      <c r="Q49" s="7" t="inlineStr"/>
       <c r="R49" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -6330,29 +6314,29 @@
       <c r="W49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>P4</t>
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>7 Later (no app uses it yet)</t>
+          <t>6 Optional monitoring</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>ADS-B Exchange</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>https://www.adsbexchange.com/</t>
+          <t>https://sentry.io/signup/</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -6367,30 +6351,38 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>DSN</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>Project → Settings → Client Keys (DSN)</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="inlineStr"/>
-      <c r="L50" s="7" t="inlineStr">
-        <is>
-          <t>PilotEnRoute; AeroSwift</t>
-        </is>
-      </c>
-      <c r="M50" s="7" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr"/>
+          <t>SENTRY_DSN define (DriftDate, NexusTransferPay)</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>DriftDate; NexusTransferPay</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>SENTRY_DSN</t>
+        </is>
+      </c>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>DriftDate: SENTRY_DSN: EMPTY in release | NexusTransferPay: SENTRY_DSN: EMPTY in release</t>
+        </is>
+      </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
@@ -6400,7 +6392,7 @@
       </c>
       <c r="Q50" s="7" t="inlineStr">
         <is>
-          <t>Signing up earns nothing until an app is built to use it</t>
+          <t>Optional — Crashlytics already covers crashes</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
@@ -6422,22 +6414,22 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>7 Later (no app uses it yet)</t>
+          <t>6 Optional monitoring</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Agoda Partner Hub</t>
+          <t>PostHog</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>https://partners.agoda.com/</t>
+          <t>https://us.posthog.com/signup</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -6447,45 +6439,45 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>Project key</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>Project settings → Project API key</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>POSTHOG_API_KEY (MyHealth)</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr"/>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>MyHealth</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr"/>
       <c r="N51" s="7" t="inlineStr"/>
       <c r="O51" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>Signing up earns nothing until an app is built to use it</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
@@ -6512,17 +6504,17 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Airalo</t>
+          <t>ADS-B Exchange</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>https://partners.airalo.com/</t>
+          <t>https://www.adsbexchange.com/</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -6532,40 +6524,40 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>PilotEnRoute; AeroSwift</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr"/>
       <c r="N52" s="7" t="inlineStr"/>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
@@ -6597,60 +6589,60 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Airplanes.Live</t>
+          <t>Agoda Partner Hub</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>https://airplanes.live/</t>
+          <t>https://partners.agoda.com/</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr"/>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>AeroSwift; PilotEnRoute</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="7" t="inlineStr"/>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
@@ -6682,42 +6674,42 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Allianz Partners</t>
+          <t>Airalo</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>https://www.allianz-partners.com/</t>
+          <t>https://partners.airalo.com/</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr"/>
@@ -6730,12 +6722,12 @@
       <c r="N54" s="7" t="inlineStr"/>
       <c r="O54" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
@@ -6767,7 +6759,7 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Alpha Vantage</t>
+          <t>Airplanes.Live</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -6777,12 +6769,12 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>https://www.alphavantage.co/support/#api-key</t>
+          <t>https://airplanes.live/</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -6808,7 +6800,7 @@
       <c r="K55" s="7" t="inlineStr"/>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>ApexMarketWatch; daily-pulse</t>
+          <t>AeroSwift; PilotEnRoute</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr"/>
@@ -6852,42 +6844,42 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Amadeus for Developers</t>
+          <t>Allianz Partners</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>https://developers.amadeus.com/register</t>
+          <t>https://www.allianz-partners.com/</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://developers.amadeus.com/</t>
+          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr"/>
@@ -6900,12 +6892,12 @@
       <c r="N56" s="7" t="inlineStr"/>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
@@ -6937,7 +6929,7 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Auth0</t>
+          <t>Alpha Vantage</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -6947,7 +6939,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>https://auth0.com/signup</t>
+          <t>https://www.alphavantage.co/support/#api-key</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -6976,7 +6968,11 @@
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr"/>
-      <c r="L57" s="7" t="inlineStr"/>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>ApexMarketWatch; daily-pulse</t>
+        </is>
+      </c>
       <c r="M57" s="7" t="inlineStr"/>
       <c r="N57" s="7" t="inlineStr"/>
       <c r="O57" s="7" t="inlineStr">
@@ -7018,7 +7014,7 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Aviationstack</t>
+          <t>Amadeus for Developers</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -7028,12 +7024,12 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>https://aviationstack.com/signup/free</t>
+          <t>https://developers.amadeus.com/register</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK (HTTP 200), lands on https://developers.amadeus.com/</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -7059,7 +7055,7 @@
       <c r="K58" s="7" t="inlineStr"/>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>AeroSwift; PilotEnRoute</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr"/>
@@ -7103,17 +7099,17 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Bounce</t>
+          <t>Auth0</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>https://bounce.com/</t>
+          <t>https://auth0.com/signup</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -7123,40 +7119,36 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr"/>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>TripNest</t>
-        </is>
-      </c>
+      <c r="L59" s="7" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
       <c r="N59" s="7" t="inlineStr"/>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
@@ -7188,60 +7180,60 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>CarTrawler</t>
+          <t>Aviationstack</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>https://www.cartrawler.com/</t>
+          <t>https://aviationstack.com/signup/free</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://corporate.cartrawler.com/en-gb/</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr"/>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>AeroSwift; PilotEnRoute</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr"/>
       <c r="N60" s="7" t="inlineStr"/>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
@@ -7273,17 +7265,17 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>CheckWX</t>
+          <t>Bounce</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>https://www.checkwxapi.com/</t>
+          <t>https://bounce.com/</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -7293,40 +7285,40 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr"/>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr"/>
       <c r="N61" s="7" t="inlineStr"/>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
@@ -7358,7 +7350,7 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Cirium</t>
+          <t>CarTrawler</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -7368,12 +7360,12 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>https://www.cirium.com/</t>
+          <t>https://www.cartrawler.com/</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK (HTTP 200), lands on https://corporate.cartrawler.com/en-gb/</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -7399,7 +7391,7 @@
       <c r="K62" s="7" t="inlineStr"/>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>AeroSwift; PilotEnRoute</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr"/>
@@ -7443,17 +7435,17 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Cover Genius</t>
+          <t>CheckWX</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>https://covergenius.com/</t>
+          <t>https://www.checkwxapi.com/</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
@@ -7463,40 +7455,40 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr"/>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>PilotEnRoute</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr"/>
       <c r="N63" s="7" t="inlineStr"/>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
@@ -7528,17 +7520,17 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>DiscoverCars</t>
+          <t>Cirium</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>https://www.discovercars.com/affiliate</t>
+          <t>https://www.cirium.com/</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -7548,40 +7540,40 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr"/>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>AeroSwift; PilotEnRoute</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr"/>
       <c r="N64" s="7" t="inlineStr"/>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
@@ -7613,7 +7605,7 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Distribusion</t>
+          <t>Cover Genius</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -7623,7 +7615,7 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>https://www.distribusion.com/</t>
+          <t>https://covergenius.com/</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -7698,17 +7690,17 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>Dragonpass</t>
+          <t>DiscoverCars</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>https://www.dragonpass.com/</t>
+          <t>https://www.discovercars.com/affiliate</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -7718,22 +7710,22 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr"/>
@@ -7746,12 +7738,12 @@
       <c r="N66" s="7" t="inlineStr"/>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
@@ -7783,17 +7775,17 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Duffel</t>
+          <t>Distribusion</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>https://app.duffel.com/join</t>
+          <t>https://www.distribusion.com/</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -7803,22 +7795,22 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr"/>
@@ -7831,12 +7823,12 @@
       <c r="N67" s="7" t="inlineStr"/>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
@@ -7868,17 +7860,17 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Edamam</t>
+          <t>Dragonpass</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>https://developer.edamam.com/</t>
+          <t>https://www.dragonpass.com/</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -7888,40 +7880,40 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr"/>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>ChefCount; GroceryMatch</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr"/>
       <c r="N68" s="7" t="inlineStr"/>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q68" s="7" t="inlineStr">
@@ -7953,7 +7945,7 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Finnhub</t>
+          <t>Duffel</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -7963,7 +7955,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>https://finnhub.io/</t>
+          <t>https://app.duffel.com/join</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -7994,7 +7986,7 @@
       <c r="K69" s="7" t="inlineStr"/>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>ApexMarketWatch; daily-pulse</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr"/>
@@ -8038,7 +8030,7 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>FlightAware AeroAPI</t>
+          <t>Edamam</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -8048,7 +8040,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>https://www.flightaware.com/aeroapi/portal</t>
+          <t>https://developer.edamam.com/</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -8079,7 +8071,7 @@
       <c r="K70" s="7" t="inlineStr"/>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute; AeroSwift</t>
+          <t>ChefCount; GroceryMatch</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr"/>
@@ -8123,17 +8115,17 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>ForeFlight</t>
+          <t>Finnhub</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>https://foreflight.com/</t>
+          <t>https://finnhub.io/</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -8143,40 +8135,40 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr"/>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute</t>
+          <t>ApexMarketWatch; daily-pulse</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr"/>
       <c r="N71" s="7" t="inlineStr"/>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q71" s="7" t="inlineStr">
@@ -8208,17 +8200,17 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Garmin Aviation</t>
+          <t>FlightAware AeroAPI</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>https://www.garmin.com/en-US/c/aviation/</t>
+          <t>https://www.flightaware.com/aeroapi/portal</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -8228,40 +8220,40 @@
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr"/>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute</t>
+          <t>PilotEnRoute; AeroSwift</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr"/>
       <c r="N72" s="7" t="inlineStr"/>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
@@ -8293,17 +8285,17 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>GetYourGuide</t>
+          <t>ForeFlight</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>https://partner.getyourguide.com/</t>
+          <t>https://foreflight.com/</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -8313,40 +8305,40 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr"/>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>TripNest; EventSpark</t>
+          <t>PilotEnRoute</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr"/>
       <c r="N73" s="7" t="inlineStr"/>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
@@ -8378,17 +8370,17 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>GNews</t>
+          <t>Garmin Aviation</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>https://gnews.io/</t>
+          <t>https://www.garmin.com/en-US/c/aviation/</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -8398,40 +8390,40 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr"/>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>daily-pulse; NewsBoard</t>
+          <t>PilotEnRoute</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr"/>
       <c r="N74" s="7" t="inlineStr"/>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
@@ -8463,7 +8455,7 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Holafly</t>
+          <t>GetYourGuide</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -8473,7 +8465,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>https://esim.holafly.com/</t>
+          <t>https://partner.getyourguide.com/</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -8504,7 +8496,7 @@
       <c r="K75" s="7" t="inlineStr"/>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>TripNest; EventSpark</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr"/>
@@ -8548,17 +8540,17 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>HomeToGo</t>
+          <t>GNews</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>https://www.hometogo.com/</t>
+          <t>https://gnews.io/</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -8568,40 +8560,40 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr"/>
       <c r="L76" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>daily-pulse; NewsBoard</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr"/>
       <c r="N76" s="7" t="inlineStr"/>
       <c r="O76" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P76" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q76" s="7" t="inlineStr">
@@ -8633,17 +8625,17 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Hotelbeds</t>
+          <t>Holafly</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>https://developer.hotelbeds.com/</t>
+          <t>https://esim.holafly.com/</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -8653,22 +8645,22 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr"/>
@@ -8681,12 +8673,12 @@
       <c r="N77" s="7" t="inlineStr"/>
       <c r="O77" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q77" s="7" t="inlineStr">
@@ -8718,7 +8710,7 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Jayride</t>
+          <t>HomeToGo</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -8728,7 +8720,7 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>https://www.jayride.com/</t>
+          <t>https://www.hometogo.com/</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -8803,7 +8795,7 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Kiwi.com Tequila</t>
+          <t>Hotelbeds</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -8813,7 +8805,7 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>https://tequila.kiwi.com/</t>
+          <t>https://developer.hotelbeds.com/</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -8888,17 +8880,17 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>LoungeKey</t>
+          <t>Jayride</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>https://www.loungekey.com/</t>
+          <t>https://www.jayride.com/</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
@@ -8908,22 +8900,22 @@
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K80" s="7" t="inlineStr"/>
@@ -8936,12 +8928,12 @@
       <c r="N80" s="7" t="inlineStr"/>
       <c r="O80" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P80" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q80" s="7" t="inlineStr">
@@ -8973,17 +8965,17 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Mapbox</t>
+          <t>Kiwi.com Tequila</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>https://account.mapbox.com/auth/signup/</t>
+          <t>https://tequila.kiwi.com/</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -8993,40 +8985,40 @@
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr"/>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>NearServe; iMaps</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr"/>
       <c r="N81" s="7" t="inlineStr"/>
       <c r="O81" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
@@ -9058,17 +9050,17 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>NewsAPI</t>
+          <t>LoungeKey</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>https://newsapi.org/register</t>
+          <t>https://www.loungekey.com/</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -9078,40 +9070,40 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K82" s="7" t="inlineStr"/>
       <c r="L82" s="7" t="inlineStr">
         <is>
-          <t>daily-pulse; NewsBoard</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr"/>
       <c r="N82" s="7" t="inlineStr"/>
       <c r="O82" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P82" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q82" s="7" t="inlineStr">
@@ -9143,60 +9135,60 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Omio</t>
+          <t>Mapbox</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>https://www.omio.com/</t>
+          <t>https://account.mapbox.com/auth/signup/</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr"/>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>NearServe; iMaps</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr"/>
       <c r="N83" s="7" t="inlineStr"/>
       <c r="O83" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
@@ -9228,7 +9220,7 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>OpenAIP</t>
+          <t>NewsAPI</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
@@ -9238,7 +9230,7 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>https://www.openaip.net/</t>
+          <t>https://newsapi.org/register</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -9269,7 +9261,7 @@
       <c r="K84" s="7" t="inlineStr"/>
       <c r="L84" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute</t>
+          <t>daily-pulse; NewsBoard</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr"/>
@@ -9313,60 +9305,60 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>OpenWeather</t>
+          <t>Omio</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>https://home.openweathermap.org/users/sign_up</t>
+          <t>https://www.omio.com/</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr"/>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute; daily-pulse</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr"/>
       <c r="N85" s="7" t="inlineStr"/>
       <c r="O85" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q85" s="7" t="inlineStr">
@@ -9398,7 +9390,7 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Polygon.io</t>
+          <t>OpenAIP</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -9408,7 +9400,7 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>https://massive.com/dashboard/signup</t>
+          <t>https://www.openaip.net/</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -9439,7 +9431,7 @@
       <c r="K86" s="7" t="inlineStr"/>
       <c r="L86" s="7" t="inlineStr">
         <is>
-          <t>ApexMarketWatch; daily-pulse</t>
+          <t>PilotEnRoute</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr"/>
@@ -9456,7 +9448,7 @@
       </c>
       <c r="Q86" s="7" t="inlineStr">
         <is>
-          <t>Polygon.io now redirects to massive.com (rebranded). Signing up earns nothing until an app is built to use it</t>
+          <t>Signing up earns nothing until an app is built to use it</t>
         </is>
       </c>
       <c r="R86" s="7" t="inlineStr">
@@ -9483,17 +9475,17 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Radical Storage</t>
+          <t>OpenWeather</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>https://radicalstorage.com/</t>
+          <t>https://home.openweathermap.org/users/sign_up</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -9503,40 +9495,40 @@
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr"/>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>PilotEnRoute; daily-pulse</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr"/>
       <c r="N87" s="7" t="inlineStr"/>
       <c r="O87" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q87" s="7" t="inlineStr">
@@ -9568,7 +9560,7 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Resend</t>
+          <t>Polygon.io</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -9578,7 +9570,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>https://resend.com/signup</t>
+          <t>https://massive.com/dashboard/signup</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -9607,7 +9599,11 @@
         </is>
       </c>
       <c r="K88" s="7" t="inlineStr"/>
-      <c r="L88" s="7" t="inlineStr"/>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>ApexMarketWatch; daily-pulse</t>
+        </is>
+      </c>
       <c r="M88" s="7" t="inlineStr"/>
       <c r="N88" s="7" t="inlineStr"/>
       <c r="O88" s="7" t="inlineStr">
@@ -9622,7 +9618,7 @@
       </c>
       <c r="Q88" s="7" t="inlineStr">
         <is>
-          <t>Signing up earns nothing until an app is built to use it</t>
+          <t>Polygon.io now redirects to massive.com (rebranded). Signing up earns nothing until an app is built to use it</t>
         </is>
       </c>
       <c r="R88" s="7" t="inlineStr">
@@ -9649,42 +9645,42 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Rome2Rio</t>
+          <t>Radical Storage</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>https://www.rome2rio.com/</t>
+          <t>https://radicalstorage.com/</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr"/>
@@ -9697,12 +9693,12 @@
       <c r="N89" s="7" t="inlineStr"/>
       <c r="O89" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
@@ -9734,17 +9730,17 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Sabre</t>
+          <t>Resend</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>https://developer.sabre.com/</t>
+          <t>https://resend.com/signup</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -9754,40 +9750,36 @@
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K90" s="7" t="inlineStr"/>
-      <c r="L90" s="7" t="inlineStr">
-        <is>
-          <t>TripNest</t>
-        </is>
-      </c>
+      <c r="L90" s="7" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
       <c r="N90" s="7" t="inlineStr"/>
       <c r="O90" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P90" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q90" s="7" t="inlineStr">
@@ -9819,56 +9811,60 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>SendGrid</t>
+          <t>Rome2Rio</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>https://signup.sendgrid.com/</t>
+          <t>https://www.rome2rio.com/</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://login.sendgrid.com/unified_login/start?screen_hint=signup</t>
+          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr"/>
-      <c r="L91" s="7" t="inlineStr"/>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>TripNest</t>
+        </is>
+      </c>
       <c r="M91" s="7" t="inlineStr"/>
       <c r="N91" s="7" t="inlineStr"/>
       <c r="O91" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
@@ -9900,7 +9896,7 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Skyscanner Partners</t>
+          <t>Sabre</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -9910,7 +9906,7 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>https://www.partners.skyscanner.net/</t>
+          <t>https://developer.sabre.com/</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -9985,7 +9981,7 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Spoonacular</t>
+          <t>SendGrid</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -9995,12 +9991,12 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>https://spoonacular.com/food-api/console#Dashboard</t>
+          <t>https://signup.sendgrid.com/</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK (HTTP 200), lands on https://login.sendgrid.com/unified_login/start?screen_hint=signup</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
@@ -10024,11 +10020,7 @@
         </is>
       </c>
       <c r="K93" s="7" t="inlineStr"/>
-      <c r="L93" s="7" t="inlineStr">
-        <is>
-          <t>ChefCount; GroceryMatch</t>
-        </is>
-      </c>
+      <c r="L93" s="7" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
       <c r="N93" s="7" t="inlineStr"/>
       <c r="O93" s="7" t="inlineStr">
@@ -10070,17 +10062,17 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Skyscanner Partners</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>https://dashboard.stripe.com/register</t>
+          <t>https://www.partners.skyscanner.net/</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -10090,36 +10082,40 @@
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr"/>
-      <c r="L94" s="7" t="inlineStr"/>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>TripNest</t>
+        </is>
+      </c>
       <c r="M94" s="7" t="inlineStr"/>
       <c r="N94" s="7" t="inlineStr"/>
       <c r="O94" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P94" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q94" s="7" t="inlineStr">
@@ -10151,7 +10147,7 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Ticketmaster Discovery API</t>
+          <t>Spoonacular</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -10161,12 +10157,12 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>https://developer-acct.ticketmaster.com/user/register</t>
+          <t>https://spoonacular.com/food-api/console#Dashboard</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://developer-account.ticketmaster.com/user/login</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
@@ -10192,7 +10188,7 @@
       <c r="K95" s="7" t="inlineStr"/>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>EventSpark</t>
+          <t>ChefCount; GroceryMatch</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr"/>
@@ -10209,7 +10205,7 @@
       </c>
       <c r="Q95" s="7" t="inlineStr">
         <is>
-          <t>The register URL lands on the developer login page — create the account from there. Signing up earns nothing until an app is built to use it</t>
+          <t>Signing up earns nothing until an app is built to use it</t>
         </is>
       </c>
       <c r="R95" s="7" t="inlineStr">
@@ -10236,7 +10232,7 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Tomorrow.io</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -10246,7 +10242,7 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>https://app.tomorrow.io/signup</t>
+          <t>https://dashboard.stripe.com/register</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -10275,11 +10271,7 @@
         </is>
       </c>
       <c r="K96" s="7" t="inlineStr"/>
-      <c r="L96" s="7" t="inlineStr">
-        <is>
-          <t>PilotEnRoute; daily-pulse</t>
-        </is>
-      </c>
+      <c r="L96" s="7" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
       <c r="N96" s="7" t="inlineStr"/>
       <c r="O96" s="7" t="inlineStr">
@@ -10321,65 +10313,65 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Trainline</t>
+          <t>Ticketmaster Discovery API</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>https://www.thetrainline.com/</t>
+          <t>https://developer-acct.ticketmaster.com/user/register</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK (HTTP 200), lands on https://developer-account.ticketmaster.com/user/login</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr"/>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>EventSpark</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr"/>
       <c r="N97" s="7" t="inlineStr"/>
       <c r="O97" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>Signing up earns nothing until an app is built to use it</t>
+          <t>The register URL lands on the developer login page — create the account from there. Signing up earns nothing until an app is built to use it</t>
         </is>
       </c>
       <c r="R97" s="7" t="inlineStr">
@@ -10406,17 +10398,17 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Travelport</t>
+          <t>Tomorrow.io</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>https://developer.travelport.com/</t>
+          <t>https://app.tomorrow.io/signup</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
@@ -10426,40 +10418,40 @@
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr"/>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>PilotEnRoute; daily-pulse</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr"/>
       <c r="N98" s="7" t="inlineStr"/>
       <c r="O98" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P98" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q98" s="7" t="inlineStr">
@@ -10491,17 +10483,17 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>VIPCars</t>
+          <t>Trainline</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>https://www.vipcars.com/</t>
+          <t>https://www.thetrainline.com/</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -10511,22 +10503,22 @@
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K99" s="7" t="inlineStr"/>
@@ -10539,12 +10531,12 @@
       <c r="N99" s="7" t="inlineStr"/>
       <c r="O99" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q99" s="7" t="inlineStr">
@@ -10576,7 +10568,7 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Wanderu</t>
+          <t>Travelport</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -10586,12 +10578,12 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>https://www.wanderu.com/</t>
+          <t>https://developer.travelport.com/</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
@@ -10661,65 +10653,61 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Welcome Pickups</t>
+          <t>USCIS FOIA</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Official USCIS FOIA portal; check developer.uscis.gov for a FOIA API</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>https://www.welcomepickups.com/</t>
+          <t>https://first.uscis.gov/</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Verify on developer.uscis.gov</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>Verify</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>If an API exists: developer portal app credentials; otherwise none (user files on the official portal)</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret if an API exists</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr"/>
-      <c r="L101" s="7" t="inlineStr">
-        <is>
-          <t>TripNest</t>
-        </is>
-      </c>
+      <c r="L101" s="7" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
       <c r="N101" s="7" t="inlineStr"/>
       <c r="O101" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Verify</t>
         </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Verify</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>Signing up earns nothing until an app is built to use it</t>
+          <t>Uscis-Case v2 FOIA helper</t>
         </is>
       </c>
       <c r="R101" s="7" t="inlineStr">
@@ -10733,10 +10721,265 @@
       <c r="V101" s="7" t="inlineStr"/>
       <c r="W101" s="7" t="inlineStr"/>
     </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>7 Later (no app uses it yet)</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>VIPCars</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Affiliate / partner programme</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>https://www.vipcars.com/</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>OK (HTTP 200)</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+        </is>
+      </c>
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>Partner/affiliate ID</t>
+        </is>
+      </c>
+      <c r="I102" s="7" t="inlineStr">
+        <is>
+          <t>Partner dashboard → your partner/affiliate ID</t>
+        </is>
+      </c>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
+          <t>Build define (public id)</t>
+        </is>
+      </c>
+      <c r="K102" s="7" t="inlineStr"/>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>TripNest</t>
+        </is>
+      </c>
+      <c r="M102" s="7" t="inlineStr"/>
+      <c r="N102" s="7" t="inlineStr"/>
+      <c r="O102" s="7" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="P102" s="7" t="inlineStr">
+        <is>
+          <t>Programme review</t>
+        </is>
+      </c>
+      <c r="Q102" s="7" t="inlineStr">
+        <is>
+          <t>Signing up earns nothing until an app is built to use it</t>
+        </is>
+      </c>
+      <c r="R102" s="7" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="S102" s="7" t="inlineStr"/>
+      <c r="T102" s="7" t="inlineStr"/>
+      <c r="U102" s="7" t="inlineStr"/>
+      <c r="V102" s="7" t="inlineStr"/>
+      <c r="W102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>7 Later (no app uses it yet)</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>Wanderu</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>Commercial partnership</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>https://www.wanderu.com/</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>Contract + API credentials</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>After contract: credentials from the account manager</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>Supabase Edge Function secret</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr"/>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>TripNest</t>
+        </is>
+      </c>
+      <c r="M103" s="7" t="inlineStr"/>
+      <c r="N103" s="7" t="inlineStr"/>
+      <c r="O103" s="7" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="P103" s="7" t="inlineStr">
+        <is>
+          <t>Weeks; sales process</t>
+        </is>
+      </c>
+      <c r="Q103" s="7" t="inlineStr">
+        <is>
+          <t>Signing up earns nothing until an app is built to use it</t>
+        </is>
+      </c>
+      <c r="R103" s="7" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="S103" s="7" t="inlineStr"/>
+      <c r="T103" s="7" t="inlineStr"/>
+      <c r="U103" s="7" t="inlineStr"/>
+      <c r="V103" s="7" t="inlineStr"/>
+      <c r="W103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>7 Later (no app uses it yet)</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Welcome Pickups</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Commercial partnership</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>https://www.welcomepickups.com/</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+        </is>
+      </c>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>Contract + API credentials</t>
+        </is>
+      </c>
+      <c r="I104" s="7" t="inlineStr">
+        <is>
+          <t>After contract: credentials from the account manager</t>
+        </is>
+      </c>
+      <c r="J104" s="7" t="inlineStr">
+        <is>
+          <t>Supabase Edge Function secret</t>
+        </is>
+      </c>
+      <c r="K104" s="7" t="inlineStr"/>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>TripNest</t>
+        </is>
+      </c>
+      <c r="M104" s="7" t="inlineStr"/>
+      <c r="N104" s="7" t="inlineStr"/>
+      <c r="O104" s="7" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="P104" s="7" t="inlineStr">
+        <is>
+          <t>Weeks; sales process</t>
+        </is>
+      </c>
+      <c r="Q104" s="7" t="inlineStr">
+        <is>
+          <t>Signing up earns nothing until an app is built to use it</t>
+        </is>
+      </c>
+      <c r="R104" s="7" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="S104" s="7" t="inlineStr"/>
+      <c r="T104" s="7" t="inlineStr"/>
+      <c r="U104" s="7" t="inlineStr"/>
+      <c r="V104" s="7" t="inlineStr"/>
+      <c r="W104" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W101"/>
+  <autoFilter ref="A1:W104"/>
   <dataValidations count="1">
-    <dataValidation sqref="R2:R101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="R2:R104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,Applied,Approved,Rejected,Done,Not needed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10756,7 +10999,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId19"/>
@@ -10836,6 +11079,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId98"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10923,7 +11169,7 @@
         </is>
       </c>
       <c r="F2">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B2,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B2,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -10955,7 +11201,7 @@
         </is>
       </c>
       <c r="F3">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B3,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B3,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -10987,7 +11233,7 @@
         </is>
       </c>
       <c r="F4">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B4,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B4,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -11019,7 +11265,7 @@
         </is>
       </c>
       <c r="F5">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B5,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B5,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -11051,7 +11297,7 @@
         </is>
       </c>
       <c r="F6">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B6,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B6,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -11083,7 +11329,7 @@
         </is>
       </c>
       <c r="F7">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B7,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B7,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -11115,7 +11361,7 @@
         </is>
       </c>
       <c r="F8">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B8,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B8,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -11147,7 +11393,7 @@
         </is>
       </c>
       <c r="F9">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B9,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B9,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -11179,7 +11425,7 @@
         </is>
       </c>
       <c r="F10">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B10,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B10,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -11211,7 +11457,7 @@
         </is>
       </c>
       <c r="F11">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B11,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B11,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -11243,7 +11489,7 @@
         </is>
       </c>
       <c r="F12">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B12,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B12,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -11275,7 +11521,7 @@
         </is>
       </c>
       <c r="F13">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B13,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B13,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -11307,7 +11553,7 @@
         </is>
       </c>
       <c r="F14">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B14,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B14,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -11339,7 +11585,7 @@
         </is>
       </c>
       <c r="F15">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B15,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B15,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -11371,7 +11617,7 @@
         </is>
       </c>
       <c r="F16">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B16,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B16,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G16" t="inlineStr">
@@ -11407,7 +11653,7 @@
         </is>
       </c>
       <c r="F17">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B17,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B17,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -11439,7 +11685,7 @@
         </is>
       </c>
       <c r="F18">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B18,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B18,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -11471,7 +11717,7 @@
         </is>
       </c>
       <c r="F19">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B19,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B19,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -11503,7 +11749,7 @@
         </is>
       </c>
       <c r="F20">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B20,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B20,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -11535,7 +11781,7 @@
         </is>
       </c>
       <c r="F21">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B21,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B21,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -11567,7 +11813,7 @@
         </is>
       </c>
       <c r="F22">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B22,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B22,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -11599,7 +11845,7 @@
         </is>
       </c>
       <c r="F23">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B23,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B23,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -11631,7 +11877,7 @@
         </is>
       </c>
       <c r="F24">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B24,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B24,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -11663,7 +11909,7 @@
         </is>
       </c>
       <c r="F25">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B25,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B25,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -11695,7 +11941,7 @@
         </is>
       </c>
       <c r="F26">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B26,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B26,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -11727,7 +11973,7 @@
         </is>
       </c>
       <c r="F27">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B27,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B27,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -11759,7 +12005,7 @@
         </is>
       </c>
       <c r="F28">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B28,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B28,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -11791,7 +12037,7 @@
         </is>
       </c>
       <c r="F29">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B29,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B29,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -11823,7 +12069,7 @@
         </is>
       </c>
       <c r="F30">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B30,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B30,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -11855,7 +12101,7 @@
         </is>
       </c>
       <c r="F31">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B31,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B31,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -11887,7 +12133,7 @@
         </is>
       </c>
       <c r="F32">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B32,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B32,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -11919,7 +12165,7 @@
         </is>
       </c>
       <c r="F33">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B33,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B33,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -11951,7 +12197,7 @@
         </is>
       </c>
       <c r="F34">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B34,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B34,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -11983,7 +12229,7 @@
         </is>
       </c>
       <c r="F35">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B35,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B35,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G35" t="inlineStr">
@@ -12019,7 +12265,7 @@
         </is>
       </c>
       <c r="F36">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B36,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B36,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G36" t="inlineStr">
@@ -12055,7 +12301,7 @@
         </is>
       </c>
       <c r="F37">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B37,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B37,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -12087,7 +12333,7 @@
         </is>
       </c>
       <c r="F38">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B38,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B38,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -12119,7 +12365,7 @@
         </is>
       </c>
       <c r="F39">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B39,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B39,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -12151,7 +12397,7 @@
         </is>
       </c>
       <c r="F40">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B40,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B40,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -12183,7 +12429,7 @@
         </is>
       </c>
       <c r="F41">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B41,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B41,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -12215,7 +12461,7 @@
         </is>
       </c>
       <c r="F42">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B42,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B42,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -12247,7 +12493,7 @@
         </is>
       </c>
       <c r="F43">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B43,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B43,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -12279,7 +12525,7 @@
         </is>
       </c>
       <c r="F44">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B44,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B44,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -12311,7 +12557,7 @@
         </is>
       </c>
       <c r="F45">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B45,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B45,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -12343,7 +12589,7 @@
         </is>
       </c>
       <c r="F46">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B46,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B46,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -12375,7 +12621,7 @@
         </is>
       </c>
       <c r="F47">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B47,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B47,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -12407,7 +12653,7 @@
         </is>
       </c>
       <c r="F48">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B48,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B48,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -12439,7 +12685,7 @@
         </is>
       </c>
       <c r="F49">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B49,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B49,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -12471,7 +12717,7 @@
         </is>
       </c>
       <c r="F50">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B50,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B50,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -12503,7 +12749,7 @@
         </is>
       </c>
       <c r="F51">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B51,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B51,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -12535,7 +12781,7 @@
         </is>
       </c>
       <c r="F52">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B52,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B52,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -12567,7 +12813,7 @@
         </is>
       </c>
       <c r="F53">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B53,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B53,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -12599,7 +12845,7 @@
         </is>
       </c>
       <c r="F54">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B54,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B54,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -12631,7 +12877,7 @@
         </is>
       </c>
       <c r="F55">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B55,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B55,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -12663,7 +12909,7 @@
         </is>
       </c>
       <c r="F56">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B56,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B56,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G56" t="inlineStr">
@@ -12699,7 +12945,7 @@
         </is>
       </c>
       <c r="F57">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B57,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B57,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G57" t="inlineStr">
@@ -12735,7 +12981,7 @@
         </is>
       </c>
       <c r="F58">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B58,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B58,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G58" t="inlineStr">
@@ -12771,7 +13017,7 @@
         </is>
       </c>
       <c r="F59">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B59,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B59,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -12803,7 +13049,7 @@
         </is>
       </c>
       <c r="F60">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B60,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B60,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -12835,7 +13081,7 @@
         </is>
       </c>
       <c r="F61">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B61,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B61,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -12867,7 +13113,7 @@
         </is>
       </c>
       <c r="F62">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B62,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B62,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G62" t="inlineStr">
@@ -12903,7 +13149,7 @@
         </is>
       </c>
       <c r="F63">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B63,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B63,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -12935,7 +13181,7 @@
         </is>
       </c>
       <c r="F64">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B64,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B64,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -12967,7 +13213,7 @@
         </is>
       </c>
       <c r="F65">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B65,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B65,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G65" t="inlineStr">
@@ -13003,7 +13249,7 @@
         </is>
       </c>
       <c r="F66">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B66,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B66,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -13035,7 +13281,7 @@
         </is>
       </c>
       <c r="F67">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B67,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B67,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -13067,7 +13313,7 @@
         </is>
       </c>
       <c r="F68">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B68,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B68,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -13099,7 +13345,7 @@
         </is>
       </c>
       <c r="F69">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B69,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B69,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -13131,7 +13377,7 @@
         </is>
       </c>
       <c r="F70">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B70,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B70,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -13163,7 +13409,7 @@
         </is>
       </c>
       <c r="F71">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B71,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B71,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -13195,7 +13441,7 @@
         </is>
       </c>
       <c r="F72">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B72,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B72,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -13227,7 +13473,7 @@
         </is>
       </c>
       <c r="F73">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B73,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B73,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -13259,7 +13505,7 @@
         </is>
       </c>
       <c r="F74">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B74,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B74,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -13291,7 +13537,7 @@
         </is>
       </c>
       <c r="F75">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B75,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B75,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -13323,7 +13569,7 @@
         </is>
       </c>
       <c r="F76">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B76,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B76,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G76" t="inlineStr">
@@ -13359,7 +13605,7 @@
         </is>
       </c>
       <c r="F77">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B77,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B77,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -13391,7 +13637,7 @@
         </is>
       </c>
       <c r="F78">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B78,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B78,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -13423,7 +13669,7 @@
         </is>
       </c>
       <c r="F79">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B79,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B79,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G79" t="inlineStr">
@@ -13459,7 +13705,7 @@
         </is>
       </c>
       <c r="F80">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B80,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B80,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G80" t="inlineStr">
@@ -13495,7 +13741,7 @@
         </is>
       </c>
       <c r="F81">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B81,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B81,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -13527,7 +13773,7 @@
         </is>
       </c>
       <c r="F82">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B82,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B82,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -13559,7 +13805,7 @@
         </is>
       </c>
       <c r="F83">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B83,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B83,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -13591,7 +13837,7 @@
         </is>
       </c>
       <c r="F84">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B84,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B84,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -13623,7 +13869,7 @@
         </is>
       </c>
       <c r="F85">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B85,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B85,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -13655,7 +13901,7 @@
         </is>
       </c>
       <c r="F86">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B86,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B86,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -13687,7 +13933,7 @@
         </is>
       </c>
       <c r="F87">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B87,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B87,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -13719,7 +13965,7 @@
         </is>
       </c>
       <c r="F88">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B88,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B88,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -13751,7 +13997,7 @@
         </is>
       </c>
       <c r="F89">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B89,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B89,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -13783,7 +14029,7 @@
         </is>
       </c>
       <c r="F90">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B90,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B90,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -13815,7 +14061,7 @@
         </is>
       </c>
       <c r="F91">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B91,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B91,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -13847,7 +14093,7 @@
         </is>
       </c>
       <c r="F92">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B92,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B92,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -13879,7 +14125,7 @@
         </is>
       </c>
       <c r="F93">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B93,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B93,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -13911,7 +14157,7 @@
         </is>
       </c>
       <c r="F94">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B94,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B94,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -13943,7 +14189,7 @@
         </is>
       </c>
       <c r="F95">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B95,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B95,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -13975,7 +14221,7 @@
         </is>
       </c>
       <c r="F96">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B96,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B96,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -14007,7 +14253,7 @@
         </is>
       </c>
       <c r="F97">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B97,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B97,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -14039,7 +14285,7 @@
         </is>
       </c>
       <c r="F98">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B98,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B98,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -14071,7 +14317,7 @@
         </is>
       </c>
       <c r="F99">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B99,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B99,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -14103,7 +14349,7 @@
         </is>
       </c>
       <c r="F100">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B100,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B100,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -14135,7 +14381,7 @@
         </is>
       </c>
       <c r="F101">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B101,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B101,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -14167,7 +14413,7 @@
         </is>
       </c>
       <c r="F102">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B102,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B102,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -14199,7 +14445,7 @@
         </is>
       </c>
       <c r="F103">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B103,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B103,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -14231,7 +14477,7 @@
         </is>
       </c>
       <c r="F104">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B104,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B104,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -14263,7 +14509,7 @@
         </is>
       </c>
       <c r="F105">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B105,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B105,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -14295,7 +14541,7 @@
         </is>
       </c>
       <c r="F106">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B106,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B106,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G106" t="inlineStr">
@@ -14331,7 +14577,7 @@
         </is>
       </c>
       <c r="F107">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B107,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B107,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -14363,7 +14609,7 @@
         </is>
       </c>
       <c r="F108">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B108,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B108,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -14395,7 +14641,7 @@
         </is>
       </c>
       <c r="F109">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B109,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B109,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -14427,7 +14673,7 @@
         </is>
       </c>
       <c r="F110">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B110,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B110,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -14459,7 +14705,7 @@
         </is>
       </c>
       <c r="F111">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B111,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B111,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -14491,7 +14737,7 @@
         </is>
       </c>
       <c r="F112">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B112,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B112,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -14523,7 +14769,7 @@
         </is>
       </c>
       <c r="F113">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B113,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B113,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -14555,7 +14801,7 @@
         </is>
       </c>
       <c r="F114">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B114,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B114,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -14587,7 +14833,7 @@
         </is>
       </c>
       <c r="F115">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B115,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B115,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -14619,7 +14865,7 @@
         </is>
       </c>
       <c r="F116">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B116,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B116,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -14651,7 +14897,7 @@
         </is>
       </c>
       <c r="F117">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B117,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B117,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -14683,7 +14929,7 @@
         </is>
       </c>
       <c r="F118">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B118,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B118,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -14715,7 +14961,7 @@
         </is>
       </c>
       <c r="F119">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B119,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B119,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -14747,7 +14993,7 @@
         </is>
       </c>
       <c r="F120">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B120,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B120,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -14779,7 +15025,7 @@
         </is>
       </c>
       <c r="F121">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B121,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B121,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -14811,7 +15057,7 @@
         </is>
       </c>
       <c r="F122">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B122,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B122,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -14843,7 +15089,7 @@
         </is>
       </c>
       <c r="F123">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B123,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B123,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -14875,7 +15121,7 @@
         </is>
       </c>
       <c r="F124">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B124,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B124,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -14907,7 +15153,7 @@
         </is>
       </c>
       <c r="F125">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B125,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B125,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -14939,7 +15185,7 @@
         </is>
       </c>
       <c r="F126">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B126,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B126,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -14971,7 +15217,7 @@
         </is>
       </c>
       <c r="F127">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B127,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B127,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -15003,7 +15249,7 @@
         </is>
       </c>
       <c r="F128">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B128,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B128,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -15035,7 +15281,7 @@
         </is>
       </c>
       <c r="F129">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B129,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B129,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -15067,7 +15313,7 @@
         </is>
       </c>
       <c r="F130">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B130,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B130,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -15099,7 +15345,7 @@
         </is>
       </c>
       <c r="F131">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B131,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B131,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -15131,7 +15377,7 @@
         </is>
       </c>
       <c r="F132">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B132,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B132,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -15163,7 +15409,7 @@
         </is>
       </c>
       <c r="F133">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B133,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B133,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -15195,7 +15441,7 @@
         </is>
       </c>
       <c r="F134">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B134,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B134,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -15227,7 +15473,7 @@
         </is>
       </c>
       <c r="F135">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B135,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B135,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -15259,7 +15505,7 @@
         </is>
       </c>
       <c r="F136">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B136,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B136,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -15291,7 +15537,7 @@
         </is>
       </c>
       <c r="F137">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B137,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B137,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -15323,7 +15569,7 @@
         </is>
       </c>
       <c r="F138">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B138,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B138,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -15355,7 +15601,7 @@
         </is>
       </c>
       <c r="F139">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B139,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B139,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -15387,7 +15633,7 @@
         </is>
       </c>
       <c r="F140">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B140,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B140,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -15419,7 +15665,7 @@
         </is>
       </c>
       <c r="F141">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B141,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B141,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -15451,7 +15697,7 @@
         </is>
       </c>
       <c r="F142">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B142,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B142,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -15483,7 +15729,7 @@
         </is>
       </c>
       <c r="F143">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B143,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B143,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -15515,7 +15761,7 @@
         </is>
       </c>
       <c r="F144">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B144,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B144,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -15547,7 +15793,7 @@
         </is>
       </c>
       <c r="F145">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B145,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B145,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -15579,7 +15825,7 @@
         </is>
       </c>
       <c r="F146">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B146,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B146,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -15611,7 +15857,7 @@
         </is>
       </c>
       <c r="F147">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B147,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B147,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -15643,7 +15889,7 @@
         </is>
       </c>
       <c r="F148">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B148,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B148,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G148" t="inlineStr">
@@ -15679,7 +15925,7 @@
         </is>
       </c>
       <c r="F149">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B149,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B149,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -15711,7 +15957,7 @@
         </is>
       </c>
       <c r="F150">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B150,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B150,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -15743,7 +15989,7 @@
         </is>
       </c>
       <c r="F151">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B151,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B151,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G151" t="inlineStr"/>
@@ -15775,7 +16021,7 @@
         </is>
       </c>
       <c r="F152">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B152,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B152,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -15807,7 +16053,7 @@
         </is>
       </c>
       <c r="F153">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B153,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B153,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G153" t="inlineStr"/>
@@ -15839,7 +16085,7 @@
         </is>
       </c>
       <c r="F154">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B154,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B154,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G154" t="inlineStr"/>
@@ -15871,7 +16117,7 @@
         </is>
       </c>
       <c r="F155">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B155,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B155,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G155" t="inlineStr"/>
@@ -15903,7 +16149,7 @@
         </is>
       </c>
       <c r="F156">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B156,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B156,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G156" t="inlineStr"/>
@@ -15935,7 +16181,7 @@
         </is>
       </c>
       <c r="F157">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B157,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B157,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G157" t="inlineStr"/>
@@ -15967,7 +16213,7 @@
         </is>
       </c>
       <c r="F158">
-        <f>IFERROR(INDEX(Signups!$R$2:$R$101,MATCH(B158,Signups!$C$2:$C$101,0)),"")</f>
+        <f>IFERROR(INDEX(Signups!$R$2:$R$104,MATCH(B158,Signups!$C$2:$C$104,0)),"")</f>
         <v/>
       </c>
       <c r="G158" t="inlineStr"/>
@@ -16045,7 +16291,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>AviationWeather.gov, eCFR, FAA DroneZone, FAA Safety Team (FAASTeam), FAA UAS, Federal Aviation Administration (FAA), Lyft, NASA ASRS, NOAA, NTSB, Open-Meteo, OpenSky Network, OurAirports, Rotate Pilot, SEC EDGAR, Uber</t>
+          <t>AviationWeather.gov, CBP I-94, eCFR, FAA DroneZone, FAA Safety Team (FAASTeam), FAA UAS, Federal Aviation Administration (FAA), Lyft, NASA ASRS, NOAA, NTSB, Open-Meteo, OpenSky Network, OurAirports, Rotate Pilot, SEC EDGAR, Uber</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -16155,7 +16401,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Anthropic, RevenueCat, OpenAI API</t>
+          <t>Anthropic, RevenueCat, USCIS Developer Portal (Case Status API), OpenAI API</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -16199,7 +16445,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ADS-B Exchange, Agoda Partner Hub, Airalo, Airplanes.Live, Allianz Partners, Alpha Vantage, Amadeus for Developers, Auth0, Aviationstack, Bounce, CarTrawler, CheckWX, Cirium, Cover Genius, DiscoverCars, Distribusion, Dragonpass, Duffel, Edamam, Finnhub, FlightAware AeroAPI, ForeFlight, Garmin Aviation, GetYourGuide, GNews, Holafly, HomeToGo, Hotelbeds, Jayride, Kiwi.com Tequila, LoungeKey, Mapbox, NewsAPI, Omio, OpenAIP, OpenWeather, Polygon.io, Radical Storage, Resend, Rome2Rio, Sabre, SendGrid, Skyscanner Partners, Spoonacular, Stripe, Ticketmaster Discovery API, Tomorrow.io, Trainline, Travelport, VIPCars, Wanderu, Welcome Pickups</t>
+          <t>ADS-B Exchange, Agoda Partner Hub, Airalo, Airplanes.Live, Allianz Partners, Alpha Vantage, Amadeus for Developers, Auth0, Aviationstack, Bounce, CarTrawler, CheckWX, Cirium, Cover Genius, DiscoverCars, Distribusion, Dragonpass, Duffel, Edamam, Finnhub, FlightAware AeroAPI, ForeFlight, Garmin Aviation, GetYourGuide, GNews, Holafly, HomeToGo, Hotelbeds, Jayride, Kiwi.com Tequila, LoungeKey, Mapbox, NewsAPI, Omio, OpenAIP, OpenWeather, Polygon.io, Radical Storage, Resend, Rome2Rio, Sabre, SendGrid, Skyscanner Partners, Spoonacular, Stripe, Ticketmaster Discovery API, Tomorrow.io, Trainline, Travelport, USCIS FOIA, VIPCars, Wanderu, Welcome Pickups</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr"/>

--- a/store/vendors/AGL_Vendor_Signup_Playbook.xlsx
+++ b/store/vendors/AGL_Vendor_Signup_Playbook.xlsx
@@ -6169,7 +6169,7 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Founder's developer.uscis.gov account (exists) → register an app → request Case Status API access</t>
+          <t>Founder's developer.uscis.gov team 'agl_developersupport' (created 2026-10-14) → register an app under the team → request Case Status API access</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>Spec: ai-office/projects/real-apps/specs/Uscis-Case-v2.md. The portal username stays in the founder vault, not in this file.</t>
+          <t>Team agl_developersupport exists (founder, 2026-10-14; page requires sign-in — HTTP 403 to an anonymous check). Next: register the Uscis-Case app under the team, request Case Status (and FOIA, if listed) API access, then put the sandbox client ID/secret into Supabase Edge Function secrets. Spec: ai-office/projects/real-apps/specs/Uscis-Case-v2.md. Portal username stays in the founder vault.</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">

--- a/store/vendors/AGL_Vendor_Signup_Playbook.xlsx
+++ b/store/vendors/AGL_Vendor_Signup_Playbook.xlsx
@@ -6218,7 +6218,7 @@
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>Team agl_developersupport exists (founder, 2026-10-14; page requires sign-in — HTTP 403 to an anonymous check). Next: register the Uscis-Case app under the team, request Case Status (and FOIA, if listed) API access, then put the sandbox client ID/secret into Supabase Edge Function secrets. Spec: ai-office/projects/real-apps/specs/Uscis-Case-v2.md. Portal username stays in the founder vault.</t>
+          <t>Team agl_developersupport: Uscis-Case app APPROVED; products enabled: 'Case Status API - Sandbox' and 'first-case-sbox' (likely the FIRST/FOIA sandbox — verify); 2 keys issued 2026-07-01, sandbox only — production access not yet requested/granted. 2026-10-14: both client secrets were pasted into a chat — ROTATE them in the portal before use. Store the new values only as Supabase Edge Function secrets (USCIS_CLIENT_ID / USCIS_CLIENT_SECRET); never in chat or git. Spec: ai-office/projects/real-apps/specs/Uscis-Case-v2.md.</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
@@ -6233,9 +6233,9 @@
       <c r="W48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>P4</t>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -6245,63 +6245,63 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>OpenAI API</t>
+          <t>USCIS FOIA</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official USCIS FOIA portal; check developer.uscis.gov for a FOIA API</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>https://platform.openai.com/signup</t>
+          <t>https://first.uscis.gov/</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>HTTP 403 to automated check — open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Verify on developer.uscis.gov</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Verify</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Dashboard → API keys → Create</t>
+          <t>If an API exists: developer portal app credentials; otherwise none (user files on the official portal)</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret if an API exists</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr"/>
-      <c r="L49" s="7" t="inlineStr">
-        <is>
-          <t>Photriya; HerJourney; daily-pulse</t>
-        </is>
-      </c>
+      <c r="L49" s="7" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
       <c r="N49" s="7" t="inlineStr"/>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>Usage-based</t>
+          <t>Verify</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
-        </is>
-      </c>
-      <c r="Q49" s="7" t="inlineStr"/>
+          <t>Verify</t>
+        </is>
+      </c>
+      <c r="Q49" s="7" t="inlineStr">
+        <is>
+          <t>The team's app has 'first-case-sbox' enabled (2026-10-14) — likely the FIRST (FOIA) sandbox API; verify its endpoints on developer.uscis.gov.</t>
+        </is>
+      </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -6314,19 +6314,19 @@
       <c r="W49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>P4</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>6 Optional monitoring</t>
+          <t>5 AI / server-side keys</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>OpenAI API</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>https://sentry.io/signup/</t>
+          <t>https://platform.openai.com/signup</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>HTTP 403 to automated check — open in a browser</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -6351,38 +6351,30 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>DSN</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>Project → Settings → Client Keys (DSN)</t>
+          <t>Dashboard → API keys → Create</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>SENTRY_DSN define (DriftDate, NexusTransferPay)</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="inlineStr">
-        <is>
-          <t>DriftDate; NexusTransferPay</t>
-        </is>
-      </c>
-      <c r="L50" s="7" t="inlineStr"/>
-      <c r="M50" s="7" t="inlineStr">
-        <is>
-          <t>SENTRY_DSN</t>
-        </is>
-      </c>
-      <c r="N50" s="7" t="inlineStr">
-        <is>
-          <t>DriftDate: SENTRY_DSN: EMPTY in release | NexusTransferPay: SENTRY_DSN: EMPTY in release</t>
-        </is>
-      </c>
+          <t>Supabase Edge Function secret — never in the app</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr"/>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>Photriya; HerJourney; daily-pulse</t>
+        </is>
+      </c>
+      <c r="M50" s="7" t="inlineStr"/>
+      <c r="N50" s="7" t="inlineStr"/>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>Free tier</t>
+          <t>Usage-based</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
@@ -6390,11 +6382,7 @@
           <t>Instant</t>
         </is>
       </c>
-      <c r="Q50" s="7" t="inlineStr">
-        <is>
-          <t>Optional — Crashlytics already covers crashes</t>
-        </is>
-      </c>
+      <c r="Q50" s="7" t="inlineStr"/>
       <c r="R50" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -6407,9 +6395,9 @@
       <c r="W50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>P4</t>
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -6419,7 +6407,7 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>PostHog</t>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -6429,7 +6417,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>https://us.posthog.com/signup</t>
+          <t>https://sentry.io/signup/</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -6444,27 +6432,35 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>Project key</t>
+          <t>DSN</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>Project settings → Project API key</t>
+          <t>Project → Settings → Client Keys (DSN)</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>POSTHOG_API_KEY (MyHealth)</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr"/>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>MyHealth</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr"/>
+          <t>SENTRY_DSN define (DriftDate, NexusTransferPay)</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>DriftDate; NexusTransferPay</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>SENTRY_DSN</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>DriftDate: SENTRY_DSN: EMPTY in release | NexusTransferPay: SENTRY_DSN: EMPTY in release</t>
+        </is>
+      </c>
       <c r="O51" s="7" t="inlineStr">
         <is>
           <t>Free tier</t>
@@ -6477,7 +6473,7 @@
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Optional — Crashlytics already covers crashes</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
@@ -6499,22 +6495,22 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>7 Later (no app uses it yet)</t>
+          <t>6 Optional monitoring</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>ADS-B Exchange</t>
+          <t>PostHog</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>https://www.adsbexchange.com/</t>
+          <t>https://us.posthog.com/signup</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -6529,30 +6525,30 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Project key</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>Project settings → Project API key</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>POSTHOG_API_KEY (MyHealth)</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute; AeroSwift</t>
+          <t>MyHealth</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr"/>
       <c r="N52" s="7" t="inlineStr"/>
       <c r="O52" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
@@ -6562,7 +6558,7 @@
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>Signing up earns nothing until an app is built to use it</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
@@ -6589,17 +6585,17 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Agoda Partner Hub</t>
+          <t>ADS-B Exchange</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>https://partners.agoda.com/</t>
+          <t>https://www.adsbexchange.com/</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -6609,40 +6605,40 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr"/>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>PilotEnRoute; AeroSwift</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="7" t="inlineStr"/>
       <c r="O53" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q53" s="7" t="inlineStr">
@@ -6674,7 +6670,7 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Airalo</t>
+          <t>Agoda Partner Hub</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -6684,7 +6680,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>https://partners.airalo.com/</t>
+          <t>https://partners.agoda.com/</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -6759,60 +6755,60 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Airplanes.Live</t>
+          <t>Airalo</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>https://airplanes.live/</t>
+          <t>https://partners.airalo.com/</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr"/>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>AeroSwift; PilotEnRoute</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr"/>
       <c r="N55" s="7" t="inlineStr"/>
       <c r="O55" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
@@ -6844,17 +6840,17 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Allianz Partners</t>
+          <t>Airplanes.Live</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>https://www.allianz-partners.com/</t>
+          <t>https://airplanes.live/</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -6864,40 +6860,40 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr"/>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>AeroSwift; PilotEnRoute</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr"/>
       <c r="N56" s="7" t="inlineStr"/>
       <c r="O56" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
@@ -6929,60 +6925,60 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Alpha Vantage</t>
+          <t>Allianz Partners</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>https://www.alphavantage.co/support/#api-key</t>
+          <t>https://www.allianz-partners.com/</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr"/>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>ApexMarketWatch; daily-pulse</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr"/>
       <c r="N57" s="7" t="inlineStr"/>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
@@ -7014,7 +7010,7 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Amadeus for Developers</t>
+          <t>Alpha Vantage</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -7024,12 +7020,12 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>https://developers.amadeus.com/register</t>
+          <t>https://www.alphavantage.co/support/#api-key</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://developers.amadeus.com/</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -7055,7 +7051,7 @@
       <c r="K58" s="7" t="inlineStr"/>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>ApexMarketWatch; daily-pulse</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr"/>
@@ -7099,7 +7095,7 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Auth0</t>
+          <t>Amadeus for Developers</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -7109,12 +7105,12 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>https://auth0.com/signup</t>
+          <t>https://developers.amadeus.com/register</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK (HTTP 200), lands on https://developers.amadeus.com/</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -7138,7 +7134,11 @@
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr"/>
-      <c r="L59" s="7" t="inlineStr"/>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>TripNest</t>
+        </is>
+      </c>
       <c r="M59" s="7" t="inlineStr"/>
       <c r="N59" s="7" t="inlineStr"/>
       <c r="O59" s="7" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Aviationstack</t>
+          <t>Auth0</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>https://aviationstack.com/signup/free</t>
+          <t>https://auth0.com/signup</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -7219,11 +7219,7 @@
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr"/>
-      <c r="L60" s="7" t="inlineStr">
-        <is>
-          <t>AeroSwift; PilotEnRoute</t>
-        </is>
-      </c>
+      <c r="L60" s="7" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
       <c r="N60" s="7" t="inlineStr"/>
       <c r="O60" s="7" t="inlineStr">
@@ -7265,17 +7261,17 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Bounce</t>
+          <t>Aviationstack</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>https://bounce.com/</t>
+          <t>https://aviationstack.com/signup/free</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -7285,40 +7281,40 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr"/>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>AeroSwift; PilotEnRoute</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr"/>
       <c r="N61" s="7" t="inlineStr"/>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
@@ -7350,42 +7346,42 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>CarTrawler</t>
+          <t>Bounce</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>https://www.cartrawler.com/</t>
+          <t>https://bounce.com/</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://corporate.cartrawler.com/en-gb/</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr"/>
@@ -7398,12 +7394,12 @@
       <c r="N62" s="7" t="inlineStr"/>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
@@ -7435,60 +7431,60 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>CheckWX</t>
+          <t>CarTrawler</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>https://www.checkwxapi.com/</t>
+          <t>https://www.cartrawler.com/</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK (HTTP 200), lands on https://corporate.cartrawler.com/en-gb/</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr"/>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr"/>
       <c r="N63" s="7" t="inlineStr"/>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
@@ -7520,17 +7516,17 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Cirium</t>
+          <t>CheckWX</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>https://www.cirium.com/</t>
+          <t>https://www.checkwxapi.com/</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -7540,40 +7536,40 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr"/>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>AeroSwift; PilotEnRoute</t>
+          <t>PilotEnRoute</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr"/>
       <c r="N64" s="7" t="inlineStr"/>
       <c r="O64" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
@@ -7605,7 +7601,7 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Cover Genius</t>
+          <t>Cirium</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -7615,7 +7611,7 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>https://covergenius.com/</t>
+          <t>https://www.cirium.com/</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -7646,7 +7642,7 @@
       <c r="K65" s="7" t="inlineStr"/>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>AeroSwift; PilotEnRoute</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr"/>
@@ -7690,17 +7686,17 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>DiscoverCars</t>
+          <t>Cover Genius</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>https://www.discovercars.com/affiliate</t>
+          <t>https://covergenius.com/</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -7710,22 +7706,22 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr"/>
@@ -7738,12 +7734,12 @@
       <c r="N66" s="7" t="inlineStr"/>
       <c r="O66" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
@@ -7775,17 +7771,17 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Distribusion</t>
+          <t>DiscoverCars</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>https://www.distribusion.com/</t>
+          <t>https://www.discovercars.com/affiliate</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -7795,22 +7791,22 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr"/>
@@ -7823,12 +7819,12 @@
       <c r="N67" s="7" t="inlineStr"/>
       <c r="O67" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
@@ -7860,7 +7856,7 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Dragonpass</t>
+          <t>Distribusion</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -7870,7 +7866,7 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>https://www.dragonpass.com/</t>
+          <t>https://www.distribusion.com/</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -7945,17 +7941,17 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Duffel</t>
+          <t>Dragonpass</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>https://app.duffel.com/join</t>
+          <t>https://www.dragonpass.com/</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -7965,22 +7961,22 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr"/>
@@ -7993,12 +7989,12 @@
       <c r="N69" s="7" t="inlineStr"/>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
@@ -8030,7 +8026,7 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Edamam</t>
+          <t>Duffel</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -8040,7 +8036,7 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>https://developer.edamam.com/</t>
+          <t>https://app.duffel.com/join</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -8071,7 +8067,7 @@
       <c r="K70" s="7" t="inlineStr"/>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>ChefCount; GroceryMatch</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr"/>
@@ -8115,7 +8111,7 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Finnhub</t>
+          <t>Edamam</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -8125,7 +8121,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>https://finnhub.io/</t>
+          <t>https://developer.edamam.com/</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -8156,7 +8152,7 @@
       <c r="K71" s="7" t="inlineStr"/>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>ApexMarketWatch; daily-pulse</t>
+          <t>ChefCount; GroceryMatch</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr"/>
@@ -8200,7 +8196,7 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>FlightAware AeroAPI</t>
+          <t>Finnhub</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -8210,7 +8206,7 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>https://www.flightaware.com/aeroapi/portal</t>
+          <t>https://finnhub.io/</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -8241,7 +8237,7 @@
       <c r="K72" s="7" t="inlineStr"/>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute; AeroSwift</t>
+          <t>ApexMarketWatch; daily-pulse</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr"/>
@@ -8285,17 +8281,17 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>ForeFlight</t>
+          <t>FlightAware AeroAPI</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>https://foreflight.com/</t>
+          <t>https://www.flightaware.com/aeroapi/portal</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -8305,40 +8301,40 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr"/>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute</t>
+          <t>PilotEnRoute; AeroSwift</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr"/>
       <c r="N73" s="7" t="inlineStr"/>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q73" s="7" t="inlineStr">
@@ -8370,7 +8366,7 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Garmin Aviation</t>
+          <t>ForeFlight</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -8380,7 +8376,7 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>https://www.garmin.com/en-US/c/aviation/</t>
+          <t>https://foreflight.com/</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -8455,17 +8451,17 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>GetYourGuide</t>
+          <t>Garmin Aviation</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>https://partner.getyourguide.com/</t>
+          <t>https://www.garmin.com/en-US/c/aviation/</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -8475,40 +8471,40 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr"/>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>TripNest; EventSpark</t>
+          <t>PilotEnRoute</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr"/>
       <c r="N75" s="7" t="inlineStr"/>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
@@ -8540,17 +8536,17 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>GNews</t>
+          <t>GetYourGuide</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>https://gnews.io/</t>
+          <t>https://partner.getyourguide.com/</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -8560,40 +8556,40 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr"/>
       <c r="L76" s="7" t="inlineStr">
         <is>
-          <t>daily-pulse; NewsBoard</t>
+          <t>TripNest; EventSpark</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr"/>
       <c r="N76" s="7" t="inlineStr"/>
       <c r="O76" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P76" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q76" s="7" t="inlineStr">
@@ -8625,17 +8621,17 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Holafly</t>
+          <t>GNews</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>https://esim.holafly.com/</t>
+          <t>https://gnews.io/</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -8645,40 +8641,40 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr"/>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>daily-pulse; NewsBoard</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr"/>
       <c r="N77" s="7" t="inlineStr"/>
       <c r="O77" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q77" s="7" t="inlineStr">
@@ -8710,7 +8706,7 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>HomeToGo</t>
+          <t>Holafly</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -8720,7 +8716,7 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>https://www.hometogo.com/</t>
+          <t>https://esim.holafly.com/</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -8795,17 +8791,17 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Hotelbeds</t>
+          <t>HomeToGo</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>https://developer.hotelbeds.com/</t>
+          <t>https://www.hometogo.com/</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -8815,22 +8811,22 @@
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr"/>
@@ -8843,12 +8839,12 @@
       <c r="N79" s="7" t="inlineStr"/>
       <c r="O79" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q79" s="7" t="inlineStr">
@@ -8880,17 +8876,17 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Jayride</t>
+          <t>Hotelbeds</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>https://www.jayride.com/</t>
+          <t>https://developer.hotelbeds.com/</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
@@ -8900,22 +8896,22 @@
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K80" s="7" t="inlineStr"/>
@@ -8928,12 +8924,12 @@
       <c r="N80" s="7" t="inlineStr"/>
       <c r="O80" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P80" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q80" s="7" t="inlineStr">
@@ -8965,17 +8961,17 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Kiwi.com Tequila</t>
+          <t>Jayride</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>https://tequila.kiwi.com/</t>
+          <t>https://www.jayride.com/</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -8985,22 +8981,22 @@
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr"/>
@@ -9013,12 +9009,12 @@
       <c r="N81" s="7" t="inlineStr"/>
       <c r="O81" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
@@ -9050,7 +9046,7 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>LoungeKey</t>
+          <t>Kiwi.com Tequila</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -9060,7 +9056,7 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>https://www.loungekey.com/</t>
+          <t>https://tequila.kiwi.com/</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -9135,17 +9131,17 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Mapbox</t>
+          <t>LoungeKey</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>https://account.mapbox.com/auth/signup/</t>
+          <t>https://www.loungekey.com/</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
@@ -9155,40 +9151,40 @@
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr"/>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>NearServe; iMaps</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr"/>
       <c r="N83" s="7" t="inlineStr"/>
       <c r="O83" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
@@ -9220,7 +9216,7 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>NewsAPI</t>
+          <t>Mapbox</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
@@ -9230,7 +9226,7 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>https://newsapi.org/register</t>
+          <t>https://account.mapbox.com/auth/signup/</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -9261,7 +9257,7 @@
       <c r="K84" s="7" t="inlineStr"/>
       <c r="L84" s="7" t="inlineStr">
         <is>
-          <t>daily-pulse; NewsBoard</t>
+          <t>NearServe; iMaps</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr"/>
@@ -9305,60 +9301,60 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Omio</t>
+          <t>NewsAPI</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>https://www.omio.com/</t>
+          <t>https://newsapi.org/register</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr"/>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>daily-pulse; NewsBoard</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr"/>
       <c r="N85" s="7" t="inlineStr"/>
       <c r="O85" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q85" s="7" t="inlineStr">
@@ -9390,60 +9386,60 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>OpenAIP</t>
+          <t>Omio</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>https://www.openaip.net/</t>
+          <t>https://www.omio.com/</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K86" s="7" t="inlineStr"/>
       <c r="L86" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr"/>
       <c r="N86" s="7" t="inlineStr"/>
       <c r="O86" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P86" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q86" s="7" t="inlineStr">
@@ -9475,7 +9471,7 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>OpenWeather</t>
+          <t>OpenAIP</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -9485,7 +9481,7 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>https://home.openweathermap.org/users/sign_up</t>
+          <t>https://www.openaip.net/</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -9516,7 +9512,7 @@
       <c r="K87" s="7" t="inlineStr"/>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute; daily-pulse</t>
+          <t>PilotEnRoute</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr"/>
@@ -9560,7 +9556,7 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Polygon.io</t>
+          <t>OpenWeather</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -9570,7 +9566,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>https://massive.com/dashboard/signup</t>
+          <t>https://home.openweathermap.org/users/sign_up</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -9601,7 +9597,7 @@
       <c r="K88" s="7" t="inlineStr"/>
       <c r="L88" s="7" t="inlineStr">
         <is>
-          <t>ApexMarketWatch; daily-pulse</t>
+          <t>PilotEnRoute; daily-pulse</t>
         </is>
       </c>
       <c r="M88" s="7" t="inlineStr"/>
@@ -9618,7 +9614,7 @@
       </c>
       <c r="Q88" s="7" t="inlineStr">
         <is>
-          <t>Polygon.io now redirects to massive.com (rebranded). Signing up earns nothing until an app is built to use it</t>
+          <t>Signing up earns nothing until an app is built to use it</t>
         </is>
       </c>
       <c r="R88" s="7" t="inlineStr">
@@ -9645,17 +9641,17 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Radical Storage</t>
+          <t>Polygon.io</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Affiliate / partner programme</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>https://radicalstorage.com/</t>
+          <t>https://massive.com/dashboard/signup</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -9665,45 +9661,45 @@
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>Partner/affiliate ID</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>Partner dashboard → your partner/affiliate ID</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>Build define (public id)</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr"/>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>ApexMarketWatch; daily-pulse</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr"/>
       <c r="N89" s="7" t="inlineStr"/>
       <c r="O89" s="7" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
-          <t>Programme review</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
         <is>
-          <t>Signing up earns nothing until an app is built to use it</t>
+          <t>Polygon.io now redirects to massive.com (rebranded). Signing up earns nothing until an app is built to use it</t>
         </is>
       </c>
       <c r="R89" s="7" t="inlineStr">
@@ -9730,17 +9726,17 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Resend</t>
+          <t>Radical Storage</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Affiliate / partner programme</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>https://resend.com/signup</t>
+          <t>https://radicalstorage.com/</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -9750,36 +9746,40 @@
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company: American Group LLC (legal name, address, EIN), contact email, website https://www.americangroup.ai, the store listing URL of each app that will carry the links, how you promote (in-app links in those apps), estimated monthly users/clicks, payout method (bank/PayPal) and US tax form W-9</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Partner/affiliate ID</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>Partner dashboard → your partner/affiliate ID</t>
         </is>
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Build define (public id)</t>
         </is>
       </c>
       <c r="K90" s="7" t="inlineStr"/>
-      <c r="L90" s="7" t="inlineStr"/>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>TripNest</t>
+        </is>
+      </c>
       <c r="M90" s="7" t="inlineStr"/>
       <c r="N90" s="7" t="inlineStr"/>
       <c r="O90" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="P90" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Programme review</t>
         </is>
       </c>
       <c r="Q90" s="7" t="inlineStr">
@@ -9811,60 +9811,56 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Rome2Rio</t>
+          <t>Resend</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>https://www.rome2rio.com/</t>
+          <t>https://resend.com/signup</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr"/>
-      <c r="L91" s="7" t="inlineStr">
-        <is>
-          <t>TripNest</t>
-        </is>
-      </c>
+      <c r="L91" s="7" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
       <c r="N91" s="7" t="inlineStr"/>
       <c r="O91" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
@@ -9896,7 +9892,7 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Sabre</t>
+          <t>Rome2Rio</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -9906,12 +9902,12 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>https://developer.sabre.com/</t>
+          <t>https://www.rome2rio.com/</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>Exists — bot-protected (Cloudflare check); open in a browser</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
@@ -9981,56 +9977,60 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>SendGrid</t>
+          <t>Sabre</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>https://signup.sendgrid.com/</t>
+          <t>https://developer.sabre.com/</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://login.sendgrid.com/unified_login/start?screen_hint=signup</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K93" s="7" t="inlineStr"/>
-      <c r="L93" s="7" t="inlineStr"/>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>TripNest</t>
+        </is>
+      </c>
       <c r="M93" s="7" t="inlineStr"/>
       <c r="N93" s="7" t="inlineStr"/>
       <c r="O93" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q93" s="7" t="inlineStr">
@@ -10062,60 +10062,56 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Skyscanner Partners</t>
+          <t>SendGrid</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>https://www.partners.skyscanner.net/</t>
+          <t>https://signup.sendgrid.com/</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK (HTTP 200), lands on https://login.sendgrid.com/unified_login/start?screen_hint=signup</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr"/>
-      <c r="L94" s="7" t="inlineStr">
-        <is>
-          <t>TripNest</t>
-        </is>
-      </c>
+      <c r="L94" s="7" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
       <c r="N94" s="7" t="inlineStr"/>
       <c r="O94" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P94" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q94" s="7" t="inlineStr">
@@ -10147,17 +10143,17 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Spoonacular</t>
+          <t>Skyscanner Partners</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Direct API account</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>https://spoonacular.com/food-api/console#Dashboard</t>
+          <t>https://www.partners.skyscanner.net/</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -10167,40 +10163,40 @@
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>API key</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
-          <t>Developer dashboard → API keys</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret — never in the app</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr"/>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>ChefCount; GroceryMatch</t>
+          <t>TripNest</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr"/>
       <c r="N95" s="7" t="inlineStr"/>
       <c r="O95" s="7" t="inlineStr">
         <is>
-          <t>Free tier / paid plans — confirm on the page</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
-          <t>Instant</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q95" s="7" t="inlineStr">
@@ -10232,7 +10228,7 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Spoonacular</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -10242,7 +10238,7 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>https://dashboard.stripe.com/register</t>
+          <t>https://spoonacular.com/food-api/console#Dashboard</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -10271,7 +10267,11 @@
         </is>
       </c>
       <c r="K96" s="7" t="inlineStr"/>
-      <c r="L96" s="7" t="inlineStr"/>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>ChefCount; GroceryMatch</t>
+        </is>
+      </c>
       <c r="M96" s="7" t="inlineStr"/>
       <c r="N96" s="7" t="inlineStr"/>
       <c r="O96" s="7" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Ticketmaster Discovery API</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>https://developer-acct.ticketmaster.com/user/register</t>
+          <t>https://dashboard.stripe.com/register</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200), lands on https://developer-account.ticketmaster.com/user/login</t>
+          <t>OK (HTTP 200)</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
@@ -10352,11 +10352,7 @@
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr"/>
-      <c r="L97" s="7" t="inlineStr">
-        <is>
-          <t>EventSpark</t>
-        </is>
-      </c>
+      <c r="L97" s="7" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
       <c r="N97" s="7" t="inlineStr"/>
       <c r="O97" s="7" t="inlineStr">
@@ -10371,7 +10367,7 @@
       </c>
       <c r="Q97" s="7" t="inlineStr">
         <is>
-          <t>The register URL lands on the developer login page — create the account from there. Signing up earns nothing until an app is built to use it</t>
+          <t>Signing up earns nothing until an app is built to use it</t>
         </is>
       </c>
       <c r="R97" s="7" t="inlineStr">
@@ -10398,7 +10394,7 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Tomorrow.io</t>
+          <t>Ticketmaster Discovery API</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -10408,12 +10404,12 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>https://app.tomorrow.io/signup</t>
+          <t>https://developer-acct.ticketmaster.com/user/register</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>OK (HTTP 200)</t>
+          <t>OK (HTTP 200), lands on https://developer-account.ticketmaster.com/user/login</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -10439,7 +10435,7 @@
       <c r="K98" s="7" t="inlineStr"/>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>PilotEnRoute; daily-pulse</t>
+          <t>EventSpark</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr"/>
@@ -10456,7 +10452,7 @@
       </c>
       <c r="Q98" s="7" t="inlineStr">
         <is>
-          <t>Signing up earns nothing until an app is built to use it</t>
+          <t>The register URL lands on the developer login page — create the account from there. Signing up earns nothing until an app is built to use it</t>
         </is>
       </c>
       <c r="R98" s="7" t="inlineStr">
@@ -10483,17 +10479,17 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Trainline</t>
+          <t>Tomorrow.io</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Commercial partnership</t>
+          <t>Direct API account</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>https://www.thetrainline.com/</t>
+          <t>https://app.tomorrow.io/signup</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -10503,40 +10499,40 @@
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
+          <t>Account email, organisation (American Group LLC), project/app name, intended use; a card for paid tiers</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Contract + API credentials</t>
+          <t>API key</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>After contract: credentials from the account manager</t>
+          <t>Developer dashboard → API keys</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret</t>
+          <t>Supabase Edge Function secret — never in the app</t>
         </is>
       </c>
       <c r="K99" s="7" t="inlineStr"/>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>TripNest</t>
+          <t>PilotEnRoute; daily-pulse</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr"/>
       <c r="N99" s="7" t="inlineStr"/>
       <c r="O99" s="7" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Free tier / paid plans — confirm on the page</t>
         </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>Weeks; sales process</t>
+          <t>Instant</t>
         </is>
       </c>
       <c r="Q99" s="7" t="inlineStr">
@@ -10568,7 +10564,7 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Travelport</t>
+          <t>Trainline</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -10578,7 +10574,7 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>https://developer.travelport.com/</t>
+          <t>https://www.thetrainline.com/</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
@@ -10653,17 +10649,17 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>USCIS FOIA</t>
+          <t>Travelport</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Official USCIS FOIA portal; check developer.uscis.gov for a FOIA API</t>
+          <t>Commercial partnership</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>https://first.uscis.gov/</t>
+          <t>https://developer.travelport.com/</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -10673,41 +10669,45 @@
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>Verify on developer.uscis.gov</t>
+          <t>Company profile, use case, expected search/booking volume, often a sales call and a signed contract before credentials</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>Verify</t>
+          <t>Contract + API credentials</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>If an API exists: developer portal app credentials; otherwise none (user files on the official portal)</t>
+          <t>After contract: credentials from the account manager</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>Supabase Edge Function secret if an API exists</t>
+          <t>Supabase Edge Function secret</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr"/>
-      <c r="L101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>TripNest</t>
+        </is>
+      </c>
       <c r="M101" s="7" t="inlineStr"/>
       <c r="N101" s="7" t="inlineStr"/>
       <c r="O101" s="7" t="inlineStr">
         <is>
-          <t>Verify</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>Verify</t>
+          <t>Weeks; sales process</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
         <is>
-          <t>Uscis-Case v2 FOIA helper</t>
+          <t>Signing up earns nothing until an app is built to use it</t>
         </is>
       </c>
       <c r="R101" s="7" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Anthropic, RevenueCat, USCIS Developer Portal (Case Status API), OpenAI API</t>
+          <t>Anthropic, RevenueCat, USCIS Developer Portal (Case Status API), USCIS FOIA, OpenAI API</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ADS-B Exchange, Agoda Partner Hub, Airalo, Airplanes.Live, Allianz Partners, Alpha Vantage, Amadeus for Developers, Auth0, Aviationstack, Bounce, CarTrawler, CheckWX, Cirium, Cover Genius, DiscoverCars, Distribusion, Dragonpass, Duffel, Edamam, Finnhub, FlightAware AeroAPI, ForeFlight, Garmin Aviation, GetYourGuide, GNews, Holafly, HomeToGo, Hotelbeds, Jayride, Kiwi.com Tequila, LoungeKey, Mapbox, NewsAPI, Omio, OpenAIP, OpenWeather, Polygon.io, Radical Storage, Resend, Rome2Rio, Sabre, SendGrid, Skyscanner Partners, Spoonacular, Stripe, Ticketmaster Discovery API, Tomorrow.io, Trainline, Travelport, USCIS FOIA, VIPCars, Wanderu, Welcome Pickups</t>
+          <t>ADS-B Exchange, Agoda Partner Hub, Airalo, Airplanes.Live, Allianz Partners, Alpha Vantage, Amadeus for Developers, Auth0, Aviationstack, Bounce, CarTrawler, CheckWX, Cirium, Cover Genius, DiscoverCars, Distribusion, Dragonpass, Duffel, Edamam, Finnhub, FlightAware AeroAPI, ForeFlight, Garmin Aviation, GetYourGuide, GNews, Holafly, HomeToGo, Hotelbeds, Jayride, Kiwi.com Tequila, LoungeKey, Mapbox, NewsAPI, Omio, OpenAIP, OpenWeather, Polygon.io, Radical Storage, Resend, Rome2Rio, Sabre, SendGrid, Skyscanner Partners, Spoonacular, Stripe, Ticketmaster Discovery API, Tomorrow.io, Trainline, Travelport, VIPCars, Wanderu, Welcome Pickups</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr"/>

--- a/store/vendors/AGL_Vendor_Signup_Playbook.xlsx
+++ b/store/vendors/AGL_Vendor_Signup_Playbook.xlsx
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PRODUCTION_DRAFT_STAGED</t>
+          <t>INTERNAL_ONLY</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Account exists: Sentry organization 'american-group-llc' (founder, 2026-10-14)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>Optional — Crashlytics already covers crashes</t>
+          <t>Org american-group-llc exists (sign-in page confirmed 2026-10-14). Only DriftDate uses Sentry today (sentry_flutter + SENTRY_DSN, empty in builds); MyHealth reads SENTRY_DSN without the SDK (dead config); NexusTransferPay no longer uses it. Next: a 'driftdate' Flutter project → DSN (public by design) passed at build time; privacy label adds crash data. Other apps use Crashlytics — no duplicate SDK.</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">

--- a/store/vendors/AGL_Vendor_Signup_Playbook.xlsx
+++ b/store/vendors/AGL_Vendor_Signup_Playbook.xlsx
@@ -5422,7 +5422,7 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>docs/admob-ids.json (already holds units)</t>
+          <t>docs/admob-ids.json (what builds pass); plan + measured checks in store/admob/ad-units-plan.csv</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr"/>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="Q39" s="7" t="inlineStr">
         <is>
-          <t>Issue #15: the AdMob apps must be created in the UI</t>
+          <t>Done 2026-10-12: 43 apps x 2 platforms x 6 formats = 516 units, all DONE; 516/516 match docs/admob-ids.json (scripts/admob_plan.py, docs/ADMOB_PLAN.md). Apps show banner/interstitial; rewarded, rewarded interstitial, native and app open units exist but most apps do not show them. AGrammarly and Kinnav ship no AdMob. Issue #15 closed.</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
@@ -5791,7 +5791,11 @@
           <t>Instant (email)</t>
         </is>
       </c>
-      <c r="Q43" s="7" t="inlineStr"/>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>MAP_KEY received 2026-10-14 (valid for FIRMS Global and US/Canada; NASA status check: 5,000 transactions / 10 min). Kept outside git at ~/agl/.secrets/nasa-firms-map-key. Not yet passed to iMaps builds.</t>
+        </is>
+      </c>
       <c r="R43" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -5940,7 +5944,7 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>NREL_API_KEY (iMaps), USDA_API_KEY</t>
+          <t>NREL_API_KEY define (iMaps; DEMO_KEY fallback today). Optional: openFDA in MyHealth (keyless works). No app reads USDA_API_KEY</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
@@ -5969,7 +5973,11 @@
           <t>Instant</t>
         </is>
       </c>
-      <c r="Q45" s="7" t="inlineStr"/>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>api.data.gov key received 2026-10-14 in chat; not stored or tested yet (AI Office judge: storing credentials is the founder's step). Store it at ~/agl/.secrets/api-data-gov-key.</t>
+        </is>
+      </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
